--- a/docs/projet/Cahier_de_recette.xlsx
+++ b/docs/projet/Cahier_de_recette.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthèse" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Scénarios'!$A$1:$L$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Scénarios'!$A$1:$L$60</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Scénarios'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -617,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2147,17 +2147,17 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Créer un bien et un bail ; activer le bail.</t>
+          <t>Créer un bien et un bail ; activer le bail ; revenir le lendemain.</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>Loyer mensuel</t>
+          <t>Loyer mensuel, prise d'effet passée</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Loyers générés depuis la prise d'effet.</t>
+          <t>Chaque nuit, loyers échus depuis la prise d'effet facturés et validés sans intervention (une facture par échéance, datée de l'échéance).</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr"/>
@@ -2631,37 +2631,37 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>R47</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>AX</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>AxisPro &gt; Grille d'évaluation</t>
+          <t>Achats et dépenses</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Importer la grille officielle ; la vérifier ; la mettre en vigueur.</t>
+          <t>Remettre en brouillon une pièce approuvée ; changer le fournisseur ; la valider.</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>Classeur du cabinet</t>
+          <t>Pièce approuvée</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>Gates, domaines, 111 critères et pièces chargés ; version 1 en vigueur.</t>
+          <t>Validation refusée : la pièce modifiée repart au circuit d'approbation.</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr"/>
@@ -2673,37 +2673,37 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>R48</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>AX</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Exploitation</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>AxisPro &gt; Dossiers</t>
+          <t>Application Rotations</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Ouvrir un dossier.</t>
+          <t>Se déconnecter ; passer en mode avion ; rouvrir l'application.</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>Projet réel anonymisé</t>
+          <t>Saisie en attente</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>Référence attribuée ; critères du premier gate à évaluer.</t>
+          <t>L'application ne s'ouvre plus sous l'identité de l'agent parti ; sa saisie en attente reste et part à sa prochaine connexion.</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr"/>
@@ -2715,7 +2715,7 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>A03</t>
+          <t>A01</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -2730,22 +2730,22 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Dossier &gt; Évaluation</t>
+          <t>AxisPro &gt; Grille d'évaluation</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Évaluer les critères ; joindre une preuve pour un critère qui l'exige.</t>
+          <t>Importer la grille officielle ; la vérifier ; la mettre en vigueur.</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Classeur du cabinet</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>Sans preuve, refus ; score et recommandation recalculés.</t>
+          <t>Gates, domaines, 111 critères et pièces chargés ; version 1 en vigueur.</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr"/>
@@ -2757,7 +2757,7 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -2772,22 +2772,22 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Dossier &gt; Synthèse</t>
+          <t>AxisPro &gt; Dossiers</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Contrôler les éliminatoires et les cinq écarts prioritaires ; passer au gate suivant.</t>
+          <t>Ouvrir un dossier.</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Projet réel anonymisé</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>NO-GO si un éliminatoire n'est pas satisfait ; passage refusé tant que le gate n'est pas évalué.</t>
+          <t>Référence attribuée ; critères du premier gate à évaluer.</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr"/>
@@ -2799,7 +2799,7 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>A05</t>
+          <t>A03</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Dossier &gt; Comités</t>
+          <t>Dossier &gt; Évaluation</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Enregistrer et verrouiller une décision ; comparer deux revues.</t>
+          <t>Évaluer les critères ; joindre une preuve pour un critère qui l'exige.</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>Décision non modifiable ; comparaison par domaine.</t>
+          <t>Sans preuve, refus ; score et recommandation recalculés.</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr"/>
@@ -2841,7 +2841,7 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>A06</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -2856,12 +2856,12 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Dossier &gt; Rapport</t>
+          <t>Dossier &gt; Synthèse</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Imprimer le rapport de décision ; l'exporter en XLSX.</t>
+          <t>Contrôler les éliminatoires et les cinq écarts prioritaires ; passer au gate suivant.</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>Politique appliquée rappelée ; pièces à fournir listées.</t>
+          <t>NO-GO si un éliminatoire n'est pas satisfait ; passage refusé tant que le gate n'est pas évalué.</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr"/>
@@ -2883,7 +2883,7 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>A05</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -2898,22 +2898,22 @@
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Dossier &gt; Temps et facturation</t>
+          <t>Dossier &gt; Comités</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Saisir des temps ; facturer les honoraires.</t>
+          <t>Enregistrer et verrouiller une décision ; comparer deux revues.</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>Taux horaire</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>Facture d'honoraires en brouillon dans la comptabilité du cabinet.</t>
+          <t>Décision non modifiable ; comparaison par domaine.</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr"/>
@@ -2925,7 +2925,7 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>A08</t>
+          <t>A06</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -2935,27 +2935,27 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Porteur de projet</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Portail</t>
+          <t>Dossier &gt; Rapport</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>Première connexion ; déposer une pièce ; écrire au cabinet.</t>
+          <t>Imprimer le rapport de décision ; l'exporter en XLSX.</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Accès ouvert par le cabinet</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>Pièce visible du cabinet ; notes internes du cabinet invisibles du porteur.</t>
+          <t>Politique appliquée rappelée ; pièces à fournir listées.</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr"/>
@@ -2967,7 +2967,7 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>A09</t>
+          <t>A07</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -2982,22 +2982,22 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Dossier &gt; Data room</t>
+          <t>Dossier &gt; Temps et facturation</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Valider une pièce ; en refuser une autre avec un motif.</t>
+          <t>Saisir des temps ; facturer les honoraires.</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Taux horaire</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>Le porteur voit l'état de chaque pièce et le motif du refus.</t>
+          <t>Facture d'honoraires en brouillon dans la comptabilité du cabinet.</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr"/>
@@ -3006,10 +3006,178 @@
       <c r="K56" s="6" t="inlineStr"/>
       <c r="L56" s="6" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>A08</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>Porteur de projet</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Portail</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>Première connexion ; déposer une pièce ; écrire au cabinet.</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>Accès ouvert par le cabinet</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>Pièce visible du cabinet ; notes internes du cabinet invisibles du porteur.</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr"/>
+      <c r="I57" s="7" t="inlineStr"/>
+      <c r="J57" s="7" t="inlineStr"/>
+      <c r="K57" s="7" t="inlineStr"/>
+      <c r="L57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Cabinet</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Dossier &gt; Data room</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>Valider une pièce ; en refuser une autre avec un motif.</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>Le porteur voit l'état de chaque pièce et le motif du refus.</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr"/>
+      <c r="I58" s="6" t="inlineStr"/>
+      <c r="J58" s="6" t="inlineStr"/>
+      <c r="K58" s="6" t="inlineStr"/>
+      <c r="L58" s="6" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>Porteur de projet</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Portail &gt; Pièces</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>Déposer un programme renommé en .pdf, puis un document Word à macros.</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>Fichiers d'essai fournis par le prestataire</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Dépôts refusés, formats acceptés rappelés (PDF, JPEG, PNG, DOCX, XLSX).</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr"/>
+      <c r="I59" s="7" t="inlineStr"/>
+      <c r="J59" s="7" t="inlineStr"/>
+      <c r="K59" s="7" t="inlineStr"/>
+      <c r="L59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Direction (société du groupe seule)</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>AxisPro Suite</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>Ouvrir AxisPro Suite avec un compte de direction ouvert à la seule société du groupe.</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>Aucun dossier, aucune pièce, revue ni grille du cabinet visible.</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr"/>
+      <c r="I60" s="6" t="inlineStr"/>
+      <c r="J60" s="6" t="inlineStr"/>
+      <c r="K60" s="6" t="inlineStr"/>
+      <c r="L60" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L56"/>
+  <autoFilter ref="A1:L60"/>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choisir OK, KO ou Réserve." type="list">
+    <dataValidation sqref="I2:I60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choisir OK, KO ou Réserve." type="list">
       <formula1>"OK,KO,Réserve"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3085,19 +3253,19 @@
         </is>
       </c>
       <c r="C2" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$56,"1")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$60,"1")</f>
         <v/>
       </c>
       <c r="D2" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"1",'Scénarios'!$I$2:$I$56,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"1",'Scénarios'!$I$2:$I$60,"OK")</f>
         <v/>
       </c>
       <c r="E2" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"1",'Scénarios'!$I$2:$I$56,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"1",'Scénarios'!$I$2:$I$60,"Réserve")</f>
         <v/>
       </c>
       <c r="F2" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"1",'Scénarios'!$I$2:$I$56,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"1",'Scénarios'!$I$2:$I$60,"KO")</f>
         <v/>
       </c>
       <c r="G2" s="9">
@@ -3117,19 +3285,19 @@
         </is>
       </c>
       <c r="C3" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$56,"2")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$60,"2")</f>
         <v/>
       </c>
       <c r="D3" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"2",'Scénarios'!$I$2:$I$56,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"2",'Scénarios'!$I$2:$I$60,"OK")</f>
         <v/>
       </c>
       <c r="E3" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"2",'Scénarios'!$I$2:$I$56,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"2",'Scénarios'!$I$2:$I$60,"Réserve")</f>
         <v/>
       </c>
       <c r="F3" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"2",'Scénarios'!$I$2:$I$56,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"2",'Scénarios'!$I$2:$I$60,"KO")</f>
         <v/>
       </c>
       <c r="G3" s="10">
@@ -3149,19 +3317,19 @@
         </is>
       </c>
       <c r="C4" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$56,"3")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$60,"3")</f>
         <v/>
       </c>
       <c r="D4" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"3",'Scénarios'!$I$2:$I$56,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"3",'Scénarios'!$I$2:$I$60,"OK")</f>
         <v/>
       </c>
       <c r="E4" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"3",'Scénarios'!$I$2:$I$56,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"3",'Scénarios'!$I$2:$I$60,"Réserve")</f>
         <v/>
       </c>
       <c r="F4" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"3",'Scénarios'!$I$2:$I$56,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"3",'Scénarios'!$I$2:$I$60,"KO")</f>
         <v/>
       </c>
       <c r="G4" s="9">
@@ -3181,19 +3349,19 @@
         </is>
       </c>
       <c r="C5" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$56,"4")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$60,"4")</f>
         <v/>
       </c>
       <c r="D5" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"4",'Scénarios'!$I$2:$I$56,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"4",'Scénarios'!$I$2:$I$60,"OK")</f>
         <v/>
       </c>
       <c r="E5" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"4",'Scénarios'!$I$2:$I$56,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"4",'Scénarios'!$I$2:$I$60,"Réserve")</f>
         <v/>
       </c>
       <c r="F5" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"4",'Scénarios'!$I$2:$I$56,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"4",'Scénarios'!$I$2:$I$60,"KO")</f>
         <v/>
       </c>
       <c r="G5" s="10">
@@ -3213,19 +3381,19 @@
         </is>
       </c>
       <c r="C6" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$56,"5")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$60,"5")</f>
         <v/>
       </c>
       <c r="D6" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"5",'Scénarios'!$I$2:$I$56,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"5",'Scénarios'!$I$2:$I$60,"OK")</f>
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"5",'Scénarios'!$I$2:$I$56,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"5",'Scénarios'!$I$2:$I$60,"Réserve")</f>
         <v/>
       </c>
       <c r="F6" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"5",'Scénarios'!$I$2:$I$56,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"5",'Scénarios'!$I$2:$I$60,"KO")</f>
         <v/>
       </c>
       <c r="G6" s="9">
@@ -3245,19 +3413,19 @@
         </is>
       </c>
       <c r="C7" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$56,"6")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$60,"6")</f>
         <v/>
       </c>
       <c r="D7" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"6",'Scénarios'!$I$2:$I$56,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"6",'Scénarios'!$I$2:$I$60,"OK")</f>
         <v/>
       </c>
       <c r="E7" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"6",'Scénarios'!$I$2:$I$56,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"6",'Scénarios'!$I$2:$I$60,"Réserve")</f>
         <v/>
       </c>
       <c r="F7" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"6",'Scénarios'!$I$2:$I$56,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"6",'Scénarios'!$I$2:$I$60,"KO")</f>
         <v/>
       </c>
       <c r="G7" s="10">
@@ -3277,19 +3445,19 @@
         </is>
       </c>
       <c r="C8" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$56,"7")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$60,"7")</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"7",'Scénarios'!$I$2:$I$56,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"7",'Scénarios'!$I$2:$I$60,"OK")</f>
         <v/>
       </c>
       <c r="E8" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"7",'Scénarios'!$I$2:$I$56,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"7",'Scénarios'!$I$2:$I$60,"Réserve")</f>
         <v/>
       </c>
       <c r="F8" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"7",'Scénarios'!$I$2:$I$56,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"7",'Scénarios'!$I$2:$I$60,"KO")</f>
         <v/>
       </c>
       <c r="G8" s="9">
@@ -3309,19 +3477,19 @@
         </is>
       </c>
       <c r="C9" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$56,"8")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$60,"8")</f>
         <v/>
       </c>
       <c r="D9" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"8",'Scénarios'!$I$2:$I$56,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"8",'Scénarios'!$I$2:$I$60,"OK")</f>
         <v/>
       </c>
       <c r="E9" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"8",'Scénarios'!$I$2:$I$56,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"8",'Scénarios'!$I$2:$I$60,"Réserve")</f>
         <v/>
       </c>
       <c r="F9" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"8",'Scénarios'!$I$2:$I$56,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"8",'Scénarios'!$I$2:$I$60,"KO")</f>
         <v/>
       </c>
       <c r="G9" s="10">
@@ -3341,19 +3509,19 @@
         </is>
       </c>
       <c r="C10" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$56,"9")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$60,"9")</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"9",'Scénarios'!$I$2:$I$56,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"9",'Scénarios'!$I$2:$I$60,"OK")</f>
         <v/>
       </c>
       <c r="E10" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"9",'Scénarios'!$I$2:$I$56,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"9",'Scénarios'!$I$2:$I$60,"Réserve")</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"9",'Scénarios'!$I$2:$I$56,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"9",'Scénarios'!$I$2:$I$60,"KO")</f>
         <v/>
       </c>
       <c r="G10" s="9">
@@ -3373,19 +3541,19 @@
         </is>
       </c>
       <c r="C11" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$56,"10")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$60,"10")</f>
         <v/>
       </c>
       <c r="D11" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"10",'Scénarios'!$I$2:$I$56,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"10",'Scénarios'!$I$2:$I$60,"OK")</f>
         <v/>
       </c>
       <c r="E11" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"10",'Scénarios'!$I$2:$I$56,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"10",'Scénarios'!$I$2:$I$60,"Réserve")</f>
         <v/>
       </c>
       <c r="F11" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"10",'Scénarios'!$I$2:$I$56,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"10",'Scénarios'!$I$2:$I$60,"KO")</f>
         <v/>
       </c>
       <c r="G11" s="10">
@@ -3405,19 +3573,19 @@
         </is>
       </c>
       <c r="C12" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$56,"11")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$60,"11")</f>
         <v/>
       </c>
       <c r="D12" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"11",'Scénarios'!$I$2:$I$56,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"11",'Scénarios'!$I$2:$I$60,"OK")</f>
         <v/>
       </c>
       <c r="E12" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"11",'Scénarios'!$I$2:$I$56,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"11",'Scénarios'!$I$2:$I$60,"Réserve")</f>
         <v/>
       </c>
       <c r="F12" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"11",'Scénarios'!$I$2:$I$56,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"11",'Scénarios'!$I$2:$I$60,"KO")</f>
         <v/>
       </c>
       <c r="G12" s="9">
@@ -3437,19 +3605,19 @@
         </is>
       </c>
       <c r="C13" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$56,"12")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$60,"12")</f>
         <v/>
       </c>
       <c r="D13" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"12",'Scénarios'!$I$2:$I$56,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"12",'Scénarios'!$I$2:$I$60,"OK")</f>
         <v/>
       </c>
       <c r="E13" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"12",'Scénarios'!$I$2:$I$56,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"12",'Scénarios'!$I$2:$I$60,"Réserve")</f>
         <v/>
       </c>
       <c r="F13" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"12",'Scénarios'!$I$2:$I$56,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"12",'Scénarios'!$I$2:$I$60,"KO")</f>
         <v/>
       </c>
       <c r="G13" s="10">
@@ -3469,19 +3637,19 @@
         </is>
       </c>
       <c r="C14" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$56,"13")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$60,"13")</f>
         <v/>
       </c>
       <c r="D14" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"13",'Scénarios'!$I$2:$I$56,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"13",'Scénarios'!$I$2:$I$60,"OK")</f>
         <v/>
       </c>
       <c r="E14" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"13",'Scénarios'!$I$2:$I$56,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"13",'Scénarios'!$I$2:$I$60,"Réserve")</f>
         <v/>
       </c>
       <c r="F14" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"13",'Scénarios'!$I$2:$I$56,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"13",'Scénarios'!$I$2:$I$60,"KO")</f>
         <v/>
       </c>
       <c r="G14" s="9">
@@ -3501,19 +3669,19 @@
         </is>
       </c>
       <c r="C15" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$56,"14")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$60,"14")</f>
         <v/>
       </c>
       <c r="D15" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"14",'Scénarios'!$I$2:$I$56,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"14",'Scénarios'!$I$2:$I$60,"OK")</f>
         <v/>
       </c>
       <c r="E15" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"14",'Scénarios'!$I$2:$I$56,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"14",'Scénarios'!$I$2:$I$60,"Réserve")</f>
         <v/>
       </c>
       <c r="F15" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"14",'Scénarios'!$I$2:$I$56,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"14",'Scénarios'!$I$2:$I$60,"KO")</f>
         <v/>
       </c>
       <c r="G15" s="10">
@@ -3533,19 +3701,19 @@
         </is>
       </c>
       <c r="C16" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$56,"15")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$60,"15")</f>
         <v/>
       </c>
       <c r="D16" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"15",'Scénarios'!$I$2:$I$56,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"15",'Scénarios'!$I$2:$I$60,"OK")</f>
         <v/>
       </c>
       <c r="E16" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"15",'Scénarios'!$I$2:$I$56,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"15",'Scénarios'!$I$2:$I$60,"Réserve")</f>
         <v/>
       </c>
       <c r="F16" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"15",'Scénarios'!$I$2:$I$56,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"15",'Scénarios'!$I$2:$I$60,"KO")</f>
         <v/>
       </c>
       <c r="G16" s="9">
@@ -3565,19 +3733,19 @@
         </is>
       </c>
       <c r="C17" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$56,"16")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$60,"16")</f>
         <v/>
       </c>
       <c r="D17" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"16",'Scénarios'!$I$2:$I$56,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"16",'Scénarios'!$I$2:$I$60,"OK")</f>
         <v/>
       </c>
       <c r="E17" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"16",'Scénarios'!$I$2:$I$56,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"16",'Scénarios'!$I$2:$I$60,"Réserve")</f>
         <v/>
       </c>
       <c r="F17" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"16",'Scénarios'!$I$2:$I$56,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"16",'Scénarios'!$I$2:$I$60,"KO")</f>
         <v/>
       </c>
       <c r="G17" s="10">
@@ -3597,19 +3765,19 @@
         </is>
       </c>
       <c r="C18" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$56,"17")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$60,"17")</f>
         <v/>
       </c>
       <c r="D18" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"17",'Scénarios'!$I$2:$I$56,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"17",'Scénarios'!$I$2:$I$60,"OK")</f>
         <v/>
       </c>
       <c r="E18" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"17",'Scénarios'!$I$2:$I$56,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"17",'Scénarios'!$I$2:$I$60,"Réserve")</f>
         <v/>
       </c>
       <c r="F18" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"17",'Scénarios'!$I$2:$I$56,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"17",'Scénarios'!$I$2:$I$60,"KO")</f>
         <v/>
       </c>
       <c r="G18" s="9">
@@ -3629,19 +3797,19 @@
         </is>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$56,"18")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$60,"18")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"18",'Scénarios'!$I$2:$I$56,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"18",'Scénarios'!$I$2:$I$60,"OK")</f>
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"18",'Scénarios'!$I$2:$I$56,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"18",'Scénarios'!$I$2:$I$60,"Réserve")</f>
         <v/>
       </c>
       <c r="F19" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"18",'Scénarios'!$I$2:$I$56,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"18",'Scénarios'!$I$2:$I$60,"KO")</f>
         <v/>
       </c>
       <c r="G19" s="10">
@@ -3661,19 +3829,19 @@
         </is>
       </c>
       <c r="C20" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$56,"19")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$60,"19")</f>
         <v/>
       </c>
       <c r="D20" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"19",'Scénarios'!$I$2:$I$56,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"19",'Scénarios'!$I$2:$I$60,"OK")</f>
         <v/>
       </c>
       <c r="E20" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"19",'Scénarios'!$I$2:$I$56,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"19",'Scénarios'!$I$2:$I$60,"Réserve")</f>
         <v/>
       </c>
       <c r="F20" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"19",'Scénarios'!$I$2:$I$56,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"19",'Scénarios'!$I$2:$I$60,"KO")</f>
         <v/>
       </c>
       <c r="G20" s="9">
@@ -3693,19 +3861,19 @@
         </is>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$56,"AX")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$60,"AX")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"AX",'Scénarios'!$I$2:$I$56,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"AX",'Scénarios'!$I$2:$I$60,"OK")</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"AX",'Scénarios'!$I$2:$I$56,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"AX",'Scénarios'!$I$2:$I$60,"Réserve")</f>
         <v/>
       </c>
       <c r="F21" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$56,"AX",'Scénarios'!$I$2:$I$56,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"AX",'Scénarios'!$I$2:$I$60,"KO")</f>
         <v/>
       </c>
       <c r="G21" s="10">

--- a/docs/projet/Cahier_de_recette.xlsx
+++ b/docs/projet/Cahier_de_recette.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthèse" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Scénarios'!$A$1:$L$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Scénarios'!$A$1:$L$62</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Scénarios'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -617,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2715,37 +2715,37 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>R49</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>AX</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Immobilier</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>AxisPro &gt; Grille d'évaluation</t>
+          <t>Immobilier &gt; Biens et baux</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Importer la grille officielle ; la vérifier ; la mettre en vigueur.</t>
+          <t>Mettre fin à un bail ; revenir le lendemain ; modifier la valeur actuelle d'un bien.</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>Classeur du cabinet</t>
+          <t>Bail en cours</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>Gates, domaines, 111 critères et pièces chargés ; version 1 en vigueur.</t>
+          <t>Loyers dus jusqu'à la fin émis, plus aucun ensuite ; bien libre ; valeur et rendement du patrimoine mis à jour.</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr"/>
@@ -2757,37 +2757,37 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>R50</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>AX</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>AxisPro &gt; Dossiers</t>
+          <t>Clôtures et contrôles</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Ouvrir un dossier.</t>
+          <t>Après une clôture mensuelle, consulter les contrôles d'intégrité.</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>Projet réel anonymisé</t>
+          <t>Mois clôturé</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>Référence attribuée ; critères du premier gate à évaluer.</t>
+          <t>Contrôles du mois écoulé et chaînage « Intactes » pour chaque journal verrouillé.</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr"/>
@@ -2799,7 +2799,7 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>A03</t>
+          <t>A01</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -2814,22 +2814,22 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Dossier &gt; Évaluation</t>
+          <t>AxisPro &gt; Grille d'évaluation</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Évaluer les critères ; joindre une preuve pour un critère qui l'exige.</t>
+          <t>Importer la grille officielle ; la vérifier ; la mettre en vigueur.</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Classeur du cabinet</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>Sans preuve, refus ; score et recommandation recalculés.</t>
+          <t>Gates, domaines, 111 critères et pièces chargés ; version 1 en vigueur.</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr"/>
@@ -2841,7 +2841,7 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -2856,22 +2856,22 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Dossier &gt; Synthèse</t>
+          <t>AxisPro &gt; Dossiers</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Contrôler les éliminatoires et les cinq écarts prioritaires ; passer au gate suivant.</t>
+          <t>Ouvrir un dossier.</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Projet réel anonymisé</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>NO-GO si un éliminatoire n'est pas satisfait ; passage refusé tant que le gate n'est pas évalué.</t>
+          <t>Référence attribuée ; critères du premier gate à évaluer.</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr"/>
@@ -2883,7 +2883,7 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>A05</t>
+          <t>A03</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -2898,12 +2898,12 @@
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Dossier &gt; Comités</t>
+          <t>Dossier &gt; Évaluation</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Enregistrer et verrouiller une décision ; comparer deux revues.</t>
+          <t>Évaluer les critères ; joindre une preuve pour un critère qui l'exige.</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>Décision non modifiable ; comparaison par domaine.</t>
+          <t>Sans preuve, refus ; score et recommandation recalculés.</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr"/>
@@ -2925,7 +2925,7 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>A06</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Dossier &gt; Rapport</t>
+          <t>Dossier &gt; Synthèse</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>Imprimer le rapport de décision ; l'exporter en XLSX.</t>
+          <t>Contrôler les éliminatoires et les cinq écarts prioritaires ; passer au gate suivant.</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>Politique appliquée rappelée ; pièces à fournir listées.</t>
+          <t>NO-GO si un éliminatoire n'est pas satisfait ; passage refusé tant que le gate n'est pas évalué.</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr"/>
@@ -2967,7 +2967,7 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>A05</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -2982,22 +2982,22 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Dossier &gt; Temps et facturation</t>
+          <t>Dossier &gt; Comités</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Saisir des temps ; facturer les honoraires.</t>
+          <t>Enregistrer et verrouiller une décision ; comparer deux revues.</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>Taux horaire</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>Facture d'honoraires en brouillon dans la comptabilité du cabinet.</t>
+          <t>Décision non modifiable ; comparaison par domaine.</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr"/>
@@ -3009,7 +3009,7 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>A08</t>
+          <t>A06</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -3019,27 +3019,27 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Porteur de projet</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Portail</t>
+          <t>Dossier &gt; Rapport</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>Première connexion ; déposer une pièce ; écrire au cabinet.</t>
+          <t>Imprimer le rapport de décision ; l'exporter en XLSX.</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Accès ouvert par le cabinet</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>Pièce visible du cabinet ; notes internes du cabinet invisibles du porteur.</t>
+          <t>Politique appliquée rappelée ; pièces à fournir listées.</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr"/>
@@ -3051,7 +3051,7 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>A09</t>
+          <t>A07</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -3066,22 +3066,22 @@
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>Dossier &gt; Data room</t>
+          <t>Dossier &gt; Temps et facturation</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Valider une pièce ; en refuser une autre avec un motif.</t>
+          <t>Saisir des temps ; facturer les honoraires.</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Taux horaire</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>Le porteur voit l'état de chaque pièce et le motif du refus.</t>
+          <t>Facture d'honoraires en brouillon dans la comptabilité du cabinet.</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr"/>
@@ -3093,7 +3093,7 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A08</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
@@ -3108,22 +3108,22 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Portail &gt; Pièces</t>
+          <t>Portail</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>Déposer un programme renommé en .pdf, puis un document Word à macros.</t>
+          <t>Première connexion ; déposer une pièce ; écrire au cabinet.</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Fichiers d'essai fournis par le prestataire</t>
+          <t>Accès ouvert par le cabinet</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>Dépôts refusés, formats acceptés rappelés (PDF, JPEG, PNG, DOCX, XLSX).</t>
+          <t>Pièce visible du cabinet ; notes internes du cabinet invisibles du porteur.</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr"/>
@@ -3135,7 +3135,7 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>A09</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -3145,17 +3145,17 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Direction (société du groupe seule)</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>AxisPro Suite</t>
+          <t>Dossier &gt; Data room</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Ouvrir AxisPro Suite avec un compte de direction ouvert à la seule société du groupe.</t>
+          <t>Valider une pièce ; en refuser une autre avec un motif.</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>Aucun dossier, aucune pièce, revue ni grille du cabinet visible.</t>
+          <t>Le porteur voit l'état de chaque pièce et le motif du refus.</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr"/>
@@ -3174,10 +3174,94 @@
       <c r="K60" s="6" t="inlineStr"/>
       <c r="L60" s="6" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>Porteur de projet</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Portail &gt; Pièces</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Déposer un programme renommé en .pdf, puis un document Word à macros.</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Fichiers d'essai fournis par le prestataire</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>Dépôts refusés, formats acceptés rappelés (PDF, JPEG, PNG, DOCX, XLSX).</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr"/>
+      <c r="I61" s="7" t="inlineStr"/>
+      <c r="J61" s="7" t="inlineStr"/>
+      <c r="K61" s="7" t="inlineStr"/>
+      <c r="L61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Direction (société du groupe seule)</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>AxisPro Suite</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>Ouvrir AxisPro Suite avec un compte de direction ouvert à la seule société du groupe.</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>Aucun dossier, aucune pièce, revue ni grille du cabinet visible.</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr"/>
+      <c r="I62" s="6" t="inlineStr"/>
+      <c r="J62" s="6" t="inlineStr"/>
+      <c r="K62" s="6" t="inlineStr"/>
+      <c r="L62" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L60"/>
+  <autoFilter ref="A1:L62"/>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choisir OK, KO ou Réserve." type="list">
+    <dataValidation sqref="I2:I62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choisir OK, KO ou Réserve." type="list">
       <formula1>"OK,KO,Réserve"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3253,19 +3337,19 @@
         </is>
       </c>
       <c r="C2" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$60,"1")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$62,"1")</f>
         <v/>
       </c>
       <c r="D2" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"1",'Scénarios'!$I$2:$I$60,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"1",'Scénarios'!$I$2:$I$62,"OK")</f>
         <v/>
       </c>
       <c r="E2" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"1",'Scénarios'!$I$2:$I$60,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"1",'Scénarios'!$I$2:$I$62,"Réserve")</f>
         <v/>
       </c>
       <c r="F2" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"1",'Scénarios'!$I$2:$I$60,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"1",'Scénarios'!$I$2:$I$62,"KO")</f>
         <v/>
       </c>
       <c r="G2" s="9">
@@ -3285,19 +3369,19 @@
         </is>
       </c>
       <c r="C3" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$60,"2")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$62,"2")</f>
         <v/>
       </c>
       <c r="D3" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"2",'Scénarios'!$I$2:$I$60,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"2",'Scénarios'!$I$2:$I$62,"OK")</f>
         <v/>
       </c>
       <c r="E3" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"2",'Scénarios'!$I$2:$I$60,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"2",'Scénarios'!$I$2:$I$62,"Réserve")</f>
         <v/>
       </c>
       <c r="F3" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"2",'Scénarios'!$I$2:$I$60,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"2",'Scénarios'!$I$2:$I$62,"KO")</f>
         <v/>
       </c>
       <c r="G3" s="10">
@@ -3317,19 +3401,19 @@
         </is>
       </c>
       <c r="C4" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$60,"3")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$62,"3")</f>
         <v/>
       </c>
       <c r="D4" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"3",'Scénarios'!$I$2:$I$60,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"3",'Scénarios'!$I$2:$I$62,"OK")</f>
         <v/>
       </c>
       <c r="E4" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"3",'Scénarios'!$I$2:$I$60,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"3",'Scénarios'!$I$2:$I$62,"Réserve")</f>
         <v/>
       </c>
       <c r="F4" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"3",'Scénarios'!$I$2:$I$60,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"3",'Scénarios'!$I$2:$I$62,"KO")</f>
         <v/>
       </c>
       <c r="G4" s="9">
@@ -3349,19 +3433,19 @@
         </is>
       </c>
       <c r="C5" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$60,"4")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$62,"4")</f>
         <v/>
       </c>
       <c r="D5" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"4",'Scénarios'!$I$2:$I$60,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"4",'Scénarios'!$I$2:$I$62,"OK")</f>
         <v/>
       </c>
       <c r="E5" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"4",'Scénarios'!$I$2:$I$60,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"4",'Scénarios'!$I$2:$I$62,"Réserve")</f>
         <v/>
       </c>
       <c r="F5" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"4",'Scénarios'!$I$2:$I$60,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"4",'Scénarios'!$I$2:$I$62,"KO")</f>
         <v/>
       </c>
       <c r="G5" s="10">
@@ -3381,19 +3465,19 @@
         </is>
       </c>
       <c r="C6" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$60,"5")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$62,"5")</f>
         <v/>
       </c>
       <c r="D6" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"5",'Scénarios'!$I$2:$I$60,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"5",'Scénarios'!$I$2:$I$62,"OK")</f>
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"5",'Scénarios'!$I$2:$I$60,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"5",'Scénarios'!$I$2:$I$62,"Réserve")</f>
         <v/>
       </c>
       <c r="F6" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"5",'Scénarios'!$I$2:$I$60,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"5",'Scénarios'!$I$2:$I$62,"KO")</f>
         <v/>
       </c>
       <c r="G6" s="9">
@@ -3413,19 +3497,19 @@
         </is>
       </c>
       <c r="C7" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$60,"6")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$62,"6")</f>
         <v/>
       </c>
       <c r="D7" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"6",'Scénarios'!$I$2:$I$60,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"6",'Scénarios'!$I$2:$I$62,"OK")</f>
         <v/>
       </c>
       <c r="E7" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"6",'Scénarios'!$I$2:$I$60,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"6",'Scénarios'!$I$2:$I$62,"Réserve")</f>
         <v/>
       </c>
       <c r="F7" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"6",'Scénarios'!$I$2:$I$60,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"6",'Scénarios'!$I$2:$I$62,"KO")</f>
         <v/>
       </c>
       <c r="G7" s="10">
@@ -3445,19 +3529,19 @@
         </is>
       </c>
       <c r="C8" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$60,"7")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$62,"7")</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"7",'Scénarios'!$I$2:$I$60,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"7",'Scénarios'!$I$2:$I$62,"OK")</f>
         <v/>
       </c>
       <c r="E8" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"7",'Scénarios'!$I$2:$I$60,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"7",'Scénarios'!$I$2:$I$62,"Réserve")</f>
         <v/>
       </c>
       <c r="F8" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"7",'Scénarios'!$I$2:$I$60,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"7",'Scénarios'!$I$2:$I$62,"KO")</f>
         <v/>
       </c>
       <c r="G8" s="9">
@@ -3477,19 +3561,19 @@
         </is>
       </c>
       <c r="C9" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$60,"8")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$62,"8")</f>
         <v/>
       </c>
       <c r="D9" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"8",'Scénarios'!$I$2:$I$60,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"8",'Scénarios'!$I$2:$I$62,"OK")</f>
         <v/>
       </c>
       <c r="E9" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"8",'Scénarios'!$I$2:$I$60,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"8",'Scénarios'!$I$2:$I$62,"Réserve")</f>
         <v/>
       </c>
       <c r="F9" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"8",'Scénarios'!$I$2:$I$60,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"8",'Scénarios'!$I$2:$I$62,"KO")</f>
         <v/>
       </c>
       <c r="G9" s="10">
@@ -3509,19 +3593,19 @@
         </is>
       </c>
       <c r="C10" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$60,"9")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$62,"9")</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"9",'Scénarios'!$I$2:$I$60,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"9",'Scénarios'!$I$2:$I$62,"OK")</f>
         <v/>
       </c>
       <c r="E10" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"9",'Scénarios'!$I$2:$I$60,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"9",'Scénarios'!$I$2:$I$62,"Réserve")</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"9",'Scénarios'!$I$2:$I$60,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"9",'Scénarios'!$I$2:$I$62,"KO")</f>
         <v/>
       </c>
       <c r="G10" s="9">
@@ -3541,19 +3625,19 @@
         </is>
       </c>
       <c r="C11" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$60,"10")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$62,"10")</f>
         <v/>
       </c>
       <c r="D11" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"10",'Scénarios'!$I$2:$I$60,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"10",'Scénarios'!$I$2:$I$62,"OK")</f>
         <v/>
       </c>
       <c r="E11" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"10",'Scénarios'!$I$2:$I$60,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"10",'Scénarios'!$I$2:$I$62,"Réserve")</f>
         <v/>
       </c>
       <c r="F11" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"10",'Scénarios'!$I$2:$I$60,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"10",'Scénarios'!$I$2:$I$62,"KO")</f>
         <v/>
       </c>
       <c r="G11" s="10">
@@ -3573,19 +3657,19 @@
         </is>
       </c>
       <c r="C12" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$60,"11")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$62,"11")</f>
         <v/>
       </c>
       <c r="D12" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"11",'Scénarios'!$I$2:$I$60,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"11",'Scénarios'!$I$2:$I$62,"OK")</f>
         <v/>
       </c>
       <c r="E12" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"11",'Scénarios'!$I$2:$I$60,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"11",'Scénarios'!$I$2:$I$62,"Réserve")</f>
         <v/>
       </c>
       <c r="F12" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"11",'Scénarios'!$I$2:$I$60,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"11",'Scénarios'!$I$2:$I$62,"KO")</f>
         <v/>
       </c>
       <c r="G12" s="9">
@@ -3605,19 +3689,19 @@
         </is>
       </c>
       <c r="C13" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$60,"12")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$62,"12")</f>
         <v/>
       </c>
       <c r="D13" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"12",'Scénarios'!$I$2:$I$60,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"12",'Scénarios'!$I$2:$I$62,"OK")</f>
         <v/>
       </c>
       <c r="E13" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"12",'Scénarios'!$I$2:$I$60,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"12",'Scénarios'!$I$2:$I$62,"Réserve")</f>
         <v/>
       </c>
       <c r="F13" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"12",'Scénarios'!$I$2:$I$60,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"12",'Scénarios'!$I$2:$I$62,"KO")</f>
         <v/>
       </c>
       <c r="G13" s="10">
@@ -3637,19 +3721,19 @@
         </is>
       </c>
       <c r="C14" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$60,"13")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$62,"13")</f>
         <v/>
       </c>
       <c r="D14" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"13",'Scénarios'!$I$2:$I$60,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"13",'Scénarios'!$I$2:$I$62,"OK")</f>
         <v/>
       </c>
       <c r="E14" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"13",'Scénarios'!$I$2:$I$60,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"13",'Scénarios'!$I$2:$I$62,"Réserve")</f>
         <v/>
       </c>
       <c r="F14" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"13",'Scénarios'!$I$2:$I$60,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"13",'Scénarios'!$I$2:$I$62,"KO")</f>
         <v/>
       </c>
       <c r="G14" s="9">
@@ -3669,19 +3753,19 @@
         </is>
       </c>
       <c r="C15" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$60,"14")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$62,"14")</f>
         <v/>
       </c>
       <c r="D15" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"14",'Scénarios'!$I$2:$I$60,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"14",'Scénarios'!$I$2:$I$62,"OK")</f>
         <v/>
       </c>
       <c r="E15" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"14",'Scénarios'!$I$2:$I$60,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"14",'Scénarios'!$I$2:$I$62,"Réserve")</f>
         <v/>
       </c>
       <c r="F15" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"14",'Scénarios'!$I$2:$I$60,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"14",'Scénarios'!$I$2:$I$62,"KO")</f>
         <v/>
       </c>
       <c r="G15" s="10">
@@ -3701,19 +3785,19 @@
         </is>
       </c>
       <c r="C16" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$60,"15")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$62,"15")</f>
         <v/>
       </c>
       <c r="D16" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"15",'Scénarios'!$I$2:$I$60,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"15",'Scénarios'!$I$2:$I$62,"OK")</f>
         <v/>
       </c>
       <c r="E16" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"15",'Scénarios'!$I$2:$I$60,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"15",'Scénarios'!$I$2:$I$62,"Réserve")</f>
         <v/>
       </c>
       <c r="F16" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"15",'Scénarios'!$I$2:$I$60,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"15",'Scénarios'!$I$2:$I$62,"KO")</f>
         <v/>
       </c>
       <c r="G16" s="9">
@@ -3733,19 +3817,19 @@
         </is>
       </c>
       <c r="C17" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$60,"16")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$62,"16")</f>
         <v/>
       </c>
       <c r="D17" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"16",'Scénarios'!$I$2:$I$60,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"16",'Scénarios'!$I$2:$I$62,"OK")</f>
         <v/>
       </c>
       <c r="E17" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"16",'Scénarios'!$I$2:$I$60,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"16",'Scénarios'!$I$2:$I$62,"Réserve")</f>
         <v/>
       </c>
       <c r="F17" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"16",'Scénarios'!$I$2:$I$60,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"16",'Scénarios'!$I$2:$I$62,"KO")</f>
         <v/>
       </c>
       <c r="G17" s="10">
@@ -3765,19 +3849,19 @@
         </is>
       </c>
       <c r="C18" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$60,"17")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$62,"17")</f>
         <v/>
       </c>
       <c r="D18" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"17",'Scénarios'!$I$2:$I$60,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"17",'Scénarios'!$I$2:$I$62,"OK")</f>
         <v/>
       </c>
       <c r="E18" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"17",'Scénarios'!$I$2:$I$60,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"17",'Scénarios'!$I$2:$I$62,"Réserve")</f>
         <v/>
       </c>
       <c r="F18" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"17",'Scénarios'!$I$2:$I$60,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"17",'Scénarios'!$I$2:$I$62,"KO")</f>
         <v/>
       </c>
       <c r="G18" s="9">
@@ -3797,19 +3881,19 @@
         </is>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$60,"18")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$62,"18")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"18",'Scénarios'!$I$2:$I$60,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"18",'Scénarios'!$I$2:$I$62,"OK")</f>
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"18",'Scénarios'!$I$2:$I$60,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"18",'Scénarios'!$I$2:$I$62,"Réserve")</f>
         <v/>
       </c>
       <c r="F19" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"18",'Scénarios'!$I$2:$I$60,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"18",'Scénarios'!$I$2:$I$62,"KO")</f>
         <v/>
       </c>
       <c r="G19" s="10">
@@ -3829,19 +3913,19 @@
         </is>
       </c>
       <c r="C20" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$60,"19")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$62,"19")</f>
         <v/>
       </c>
       <c r="D20" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"19",'Scénarios'!$I$2:$I$60,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"19",'Scénarios'!$I$2:$I$62,"OK")</f>
         <v/>
       </c>
       <c r="E20" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"19",'Scénarios'!$I$2:$I$60,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"19",'Scénarios'!$I$2:$I$62,"Réserve")</f>
         <v/>
       </c>
       <c r="F20" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"19",'Scénarios'!$I$2:$I$60,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"19",'Scénarios'!$I$2:$I$62,"KO")</f>
         <v/>
       </c>
       <c r="G20" s="9">
@@ -3861,19 +3945,19 @@
         </is>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$60,"AX")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$62,"AX")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"AX",'Scénarios'!$I$2:$I$60,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"AX",'Scénarios'!$I$2:$I$62,"OK")</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"AX",'Scénarios'!$I$2:$I$60,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"AX",'Scénarios'!$I$2:$I$62,"Réserve")</f>
         <v/>
       </c>
       <c r="F21" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$60,"AX",'Scénarios'!$I$2:$I$60,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"AX",'Scénarios'!$I$2:$I$62,"KO")</f>
         <v/>
       </c>
       <c r="G21" s="10">

--- a/docs/projet/Cahier_de_recette.xlsx
+++ b/docs/projet/Cahier_de_recette.xlsx
@@ -2483,7 +2483,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Restaurer la production à un instant choisi dans un environnement jetable.</t>
+          <t>Restaurer la production à un instant choisi dans un environnement jetable (backup/restore-test.sh --target … --report).</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Base restaurée et contrôlée (sociétés, pièces) ; compte rendu remis.</t>
+          <t>Base restaurée et contrôlée (sociétés, pièces) ; compte rendu remis ; disponibilité du mois écoulé calculée (availability-report.py).</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr"/>
@@ -2567,17 +2567,17 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Déclarer une anomalie de recette.</t>
+          <t>Déclarer une anomalie de recette selon la procédure de support.</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Procédure de support remise</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>Prise en compte dans les délais de l'offre (chapitre 7.2).</t>
+          <t>Accusé de réception, gravité confirmée, prise en compte dans les délais de l'offre (chapitre 7.2).</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr"/>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Installer une évolution en recette, la faire valider, la mettre en production.</t>
+          <t>Ajouter une fonction ou un module du noyau selon le dossier technique, l'installer en recette, la faire valider, la mettre en production.</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Dossier technique</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>Gates, domaines, 111 critères et pièces chargés ; version 1 en vigueur.</t>
+          <t>8 gates et leurs règles, 15 domaines, 111 critères (9 knock-outs), 42 pièces et 102 rattachements chargés ; version en vigueur.</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr"/>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Évaluer les critères ; joindre une preuve pour un critère qui l'exige.</t>
+          <t>Évaluer les critères en saisie guidée ; déclarer disponible un knock-out sans pièce, puis lui joindre une preuve avec sa date de validité.</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>Sans preuve, refus ; score et recommandation recalculés.</t>
+          <t>Sans pièce, critère retenu « incomplet » (saisie inchangée) ; avec la preuve, retenu disponible ; Readiness, APD et Bankability recalculés ; pièce de la data room disponible.</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr"/>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>Contrôler les éliminatoires et les cinq écarts prioritaires ; passer au gate suivant.</t>
+          <t>Contrôler les knock-outs et les actions prioritaires ; passer au gate suivant ; forcer un passage refusé avec un motif.</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>NO-GO si un éliminatoire n'est pas satisfait ; passage refusé tant que le gate n'est pas évalué.</t>
+          <t>NO-GO si un knock-out est actif ; passage refusé avec ses motifs ; passage forcé inscrit au journal.</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr"/>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Enregistrer et verrouiller une décision ; comparer deux revues.</t>
+          <t>Sceller et verrouiller une décision HOLD motivée ; vérifier l'empreinte ; tenter de modifier le dossier ; ouvrir une nouvelle révision ; comparer deux revues.</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>Décision non modifiable ; comparaison par domaine.</t>
+          <t>Décision non modifiable, empreinte valide ; dossier figé jusqu'à la nouvelle révision ; comparaison des scores, gates et domaines.</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>Imprimer le rapport de décision ; l'exporter en XLSX.</t>
+          <t>Télécharger le rapport du comité (PDF), le classeur d'évaluation, la fiche d'évaluation (la modifier puis la réimporter), la data room (.zip) et les pièces à fournir.</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>Politique appliquée rappelée ; pièces à fournir listées.</t>
+          <t>Politique appliquée et empreinte rappelées ; classeur au plan du modèle du cabinet ; import précédé d'un aperçu des changements.</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr"/>

--- a/docs/projet/Cahier_de_recette.xlsx
+++ b/docs/projet/Cahier_de_recette.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthèse" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Scénarios'!$A$1:$L$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Scénarios'!$A$1:$L$74</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Scénarios'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -617,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L62"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Importer un relevé bancaire réel (CSV ou XLSX).</t>
+          <t>Importer un relevé bancaire réel (CSV, XLSX ou camt.053 XML) ; réimporter le même fichier.</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Lignes importées, doublons refusés, solde conforme au relevé.</t>
+          <t>Lignes importées, soldes initial et final lus et contrôlés (écart refusé sauf confirmation), doublons ignorés à la réimportation.</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr"/>
@@ -2799,37 +2799,37 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>R51</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>AX</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>AxisPro &gt; Grille d'évaluation</t>
+          <t>Balance et états &gt; Consolidé du groupe</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Importer la grille officielle ; la vérifier ; la mettre en vigueur.</t>
+          <t>Facturer une prestation d'une société du groupe à l'autre ; afficher le consolidé de l'exercice.</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>Classeur du cabinet</t>
+          <t>Facture intra-groupe</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>8 gates et leurs règles, 15 domaines, 111 critères (9 knock-outs), 42 pièces et 102 rattachements chargés ; version en vigueur.</t>
+          <t>Compte de résultat et bilan par société ; la vente et l'achat réciproques, la créance et la dette s'éliminent ; colonne Groupe = somme des sociétés − éliminations.</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr"/>
@@ -2841,37 +2841,37 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>R52</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>AX</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>AxisPro &gt; Dossiers</t>
+          <t>Finance &gt; Tableau de bord</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Ouvrir un dossier.</t>
+          <t>Choisir une date d'arrêté ; lire les onze questions du dirigeant et le bloc « Ce qui demande une décision » ; imprimer.</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Projet réel anonymisé</t>
+          <t>Données reprises</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>Référence attribuée ; critères du premier gate à évaluer.</t>
+          <t>Chaque question a sa réponse, son verdict (vert, orange, rouge) et sa lecture ; décisions reliées aux alertes.</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr"/>
@@ -2883,27 +2883,27 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>A03</t>
+          <t>R53</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>AX</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Dossier &gt; Évaluation</t>
+          <t>Pilotage &gt; Alertes</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Évaluer les critères en saisie guidée ; déclarer disponible un knock-out sans pièce, puis lui joindre une preuve avec sa date de validité.</t>
+          <t>Afficher toutes les règles, conformes comprises ; modifier un seuil (DSCR, délai de recouvrement).</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>Sans pièce, critère retenu « incomplet » (saisie inchangée) ; avec la preuve, retenu disponible ; Readiness, APD et Bankability recalculés ; pièce de la data room disponible.</t>
+          <t>Gravité, valeur, seuil et action recommandée pour chaque règle ; seuil laissé à zéro signalé en vigilance.</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr"/>
@@ -2925,37 +2925,37 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>R54</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>AX</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Dossier &gt; Synthèse</t>
+          <t>Achats et dépenses</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>Contrôler les knock-outs et les actions prioritaires ; passer au gate suivant ; forcer un passage refusé avec un motif.</t>
+          <t>Saisir une dépense par sa catégorie, sur deux axes (activité et ensemble routier).</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Catégorie Carburant</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>NO-GO si un knock-out est actif ; passage refusé avec ses motifs ; passage forcé inscrit au journal.</t>
+          <t>Compte de charge, compte du fournisseur et TVA déduits de la catégorie ; ventilation analytique sur les deux axes.</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr"/>
@@ -2967,37 +2967,37 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>A05</t>
+          <t>R55</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>AX</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Dossier &gt; Comités</t>
+          <t>Activités et budget &gt; Budget</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Sceller et verrouiller une décision HOLD motivée ; vérifier l'empreinte ; tenter de modifier le dossier ; ouvrir une nouvelle révision ; comparer deux revues.</t>
+          <t>Importer le budget par ligne budgétaire (XLSX) ; comparer au réalisé et aux engagements.</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Budget 2026 du classeur</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>Décision non modifiable, empreinte valide ; dossier figé jusqu'à la nouvelle révision ; comparaison des scores, gates et domaines.</t>
+          <t>Budget cumulé, réalisé, engagé, disponible, écart et statut (dépassement, conforme, sous-réalisation) par ligne.</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr"/>
@@ -3009,37 +3009,37 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>A06</t>
+          <t>R56</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>AX</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Chantiers puis finance et direction</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Dossier &gt; Rapport</t>
+          <t>Engagements</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>Télécharger le rapport du comité (PDF), le classeur d'évaluation, la fiche d'évaluation (la modifier puis la réimporter), la data room (.zip) et les pièces à fournir.</t>
+          <t>Créer un engagement de dépense de 60 M GNF avec son devis ; le faire approuver ; saisir ensuite la facture du fournisseur.</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Devis joint</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>Politique appliquée et empreinte rappelées ; classeur au plan du modèle du cabinet ; import précédé d'un aperçu des changements.</t>
+          <t>Engagement approuvé par la finance puis la direction ; la facture consomme l'engagement sans refaire le circuit ; reste à engager à jour.</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr"/>
@@ -3051,37 +3051,37 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>R57</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>AX</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Finance puis direction</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>Dossier &gt; Temps et facturation</t>
+          <t>Trésorerie</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Saisir des temps ; facturer les honoraires.</t>
+          <t>Saisir une sortie de banque de 150 M GNF ; tenter de la comptabiliser.</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>Taux horaire</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>Facture d'honoraires en brouillon dans la comptabilité du cabinet.</t>
+          <t>Opération en brouillon jusqu'à l'accord de la direction, comptabilisée à la dernière approbation.</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr"/>
@@ -3093,37 +3093,37 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>A08</t>
+          <t>R58</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>AX</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Porteur de projet</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Portail</t>
+          <t>Clôtures et contrôles &gt; Clôture mensuelle</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>Première connexion ; déposer une pièce ; écrire au cabinet.</t>
+          <t>Clôturer un mois complet.</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Accès ouvert par le cabinet</t>
+          <t>Mois repris</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>Pièce visible du cabinet ; notes internes du cabinet invisibles du porteur.</t>
+          <t>Dotations, liquidation de la TVA (pièce TVA du mois), factures à établir des rotations non facturées (extournées le mois suivant), sceau et procès-verbal imprimé.</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr"/>
@@ -3135,37 +3135,37 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>A09</t>
+          <t>R59</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>AX</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Finance et responsable financier</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>Dossier &gt; Data room</t>
+          <t>Clôtures et contrôles &gt; Validation de la reprise</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Valider une pièce ; en refuser une autre avec un motif.</t>
+          <t>Charger les valeurs de référence du classeur ; lancer le contrôle ; imprimer l'annexe.</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Valeurs de référence du classeur</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>Le porteur voit l'état de chaque pièce et le motif du refus.</t>
+          <t>26 indicateurs recalculés, écart de chacun ; « 26/26 » conformes attendu avant la bascule ; annexe jointe au procès-verbal de bascule.</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr"/>
@@ -3177,37 +3177,37 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>R60</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>AX</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Porteur de projet</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Portail &gt; Pièces</t>
+          <t>Transport &gt; Rentabilité</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>Déposer un programme renommé en .pdf, puis un document Word à macros.</t>
+          <t>Afficher la rentabilité par ensemble routier avec les charges de structure ; contrôler les manquants d'une rotation.</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>Fichiers d'essai fournis par le prestataire</t>
+          <t>Rotations reprises</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>Dépôts refusés, formats acceptés rappelés (PDF, JPEG, PNG, DOCX, XLSX).</t>
+          <t>Coût et CA au km, structure, résultat net par ensemble ; manquant toléré, excédentaire déduit ou imputé au chauffeur ; taxes spécifiques au barème.</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr"/>
@@ -3219,37 +3219,37 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>R61</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>AX</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Direction (société du groupe seule)</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>AxisPro Suite</t>
+          <t>Fiscalité</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Ouvrir AxisPro Suite avec un compte de direction ouvert à la seule société du groupe.</t>
+          <t>Saisir une facture fournisseur soumise à retenue à la source ; consulter la déclaration du mois.</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Prestataire non résident ou retenue BIC</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>Aucun dossier, aucune pièce, revue ni grille du cabinet visible.</t>
+          <t>Retenue calculée et portée au compte de l'État ; déclaration et historique à jour.</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr"/>
@@ -3258,10 +3258,514 @@
       <c r="K62" s="6" t="inlineStr"/>
       <c r="L62" s="6" t="inlineStr"/>
     </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>R62</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Pilotage &gt; Trésorerie</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Afficher les flux mensuels et la prévision ; régler une échéance d'emprunt depuis une ligne de relevé.</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Emprunt repris</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Encaissements, décaissements, cash net et solde par mois face au seuil ; échéance proposée au rapprochement, capital et intérêts comptabilisés une seule fois.</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr"/>
+      <c r="I63" s="7" t="inlineStr"/>
+      <c r="J63" s="7" t="inlineStr"/>
+      <c r="K63" s="7" t="inlineStr"/>
+      <c r="L63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Cabinet</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>AxisPro &gt; Grille d'évaluation</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>Importer la grille officielle ; la vérifier ; la mettre en vigueur.</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>Classeur du cabinet</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>8 gates et leurs règles, 15 domaines, 111 critères (9 knock-outs), 42 pièces et 102 rattachements chargés ; version en vigueur.</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr"/>
+      <c r="I64" s="6" t="inlineStr"/>
+      <c r="J64" s="6" t="inlineStr"/>
+      <c r="K64" s="6" t="inlineStr"/>
+      <c r="L64" s="6" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>Cabinet</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>AxisPro &gt; Dossiers</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>Ouvrir un dossier.</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>Projet réel anonymisé</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Référence attribuée ; critères du premier gate à évaluer.</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr"/>
+      <c r="I65" s="7" t="inlineStr"/>
+      <c r="J65" s="7" t="inlineStr"/>
+      <c r="K65" s="7" t="inlineStr"/>
+      <c r="L65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>A03</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Cabinet</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>Dossier &gt; Évaluation</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>Évaluer les critères en saisie guidée ; déclarer disponible un knock-out sans pièce, puis lui joindre une preuve avec sa date de validité.</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>Sans pièce, critère retenu « incomplet » (saisie inchangée) ; avec la preuve, retenu disponible ; Readiness, APD et Bankability recalculés ; pièce de la data room disponible.</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr"/>
+      <c r="I66" s="6" t="inlineStr"/>
+      <c r="J66" s="6" t="inlineStr"/>
+      <c r="K66" s="6" t="inlineStr"/>
+      <c r="L66" s="6" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>Cabinet</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Dossier &gt; Synthèse</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>Contrôler les knock-outs et les actions prioritaires ; passer au gate suivant ; forcer un passage refusé avec un motif.</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>NO-GO si un knock-out est actif ; passage refusé avec ses motifs ; passage forcé inscrit au journal.</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr"/>
+      <c r="I67" s="7" t="inlineStr"/>
+      <c r="J67" s="7" t="inlineStr"/>
+      <c r="K67" s="7" t="inlineStr"/>
+      <c r="L67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Cabinet</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Dossier &gt; Comités</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>Sceller et verrouiller une décision HOLD motivée ; vérifier l'empreinte ; tenter de modifier le dossier ; ouvrir une nouvelle révision ; comparer deux revues.</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>Décision non modifiable, empreinte valide ; dossier figé jusqu'à la nouvelle révision ; comparaison des scores, gates et domaines.</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr"/>
+      <c r="I68" s="6" t="inlineStr"/>
+      <c r="J68" s="6" t="inlineStr"/>
+      <c r="K68" s="6" t="inlineStr"/>
+      <c r="L68" s="6" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>Cabinet</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Dossier &gt; Rapport</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>Télécharger le rapport du comité (PDF), le classeur d'évaluation, la fiche d'évaluation (la modifier puis la réimporter), la data room (.zip) et les pièces à fournir.</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Politique appliquée et empreinte rappelées ; classeur au plan du modèle du cabinet ; import précédé d'un aperçu des changements.</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr"/>
+      <c r="I69" s="7" t="inlineStr"/>
+      <c r="J69" s="7" t="inlineStr"/>
+      <c r="K69" s="7" t="inlineStr"/>
+      <c r="L69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>A07</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Cabinet</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>Dossier &gt; Temps et facturation</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>Saisir des temps ; facturer les honoraires.</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>Taux horaire</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>Facture d'honoraires en brouillon dans la comptabilité du cabinet.</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr"/>
+      <c r="I70" s="6" t="inlineStr"/>
+      <c r="J70" s="6" t="inlineStr"/>
+      <c r="K70" s="6" t="inlineStr"/>
+      <c r="L70" s="6" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>A08</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>Porteur de projet</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Portail</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Première connexion ; déposer une pièce ; écrire au cabinet.</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>Accès ouvert par le cabinet</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Pièce visible du cabinet ; notes internes du cabinet invisibles du porteur.</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr"/>
+      <c r="I71" s="7" t="inlineStr"/>
+      <c r="J71" s="7" t="inlineStr"/>
+      <c r="K71" s="7" t="inlineStr"/>
+      <c r="L71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Cabinet</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>Dossier &gt; Data room</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>Valider une pièce ; en refuser une autre avec un motif.</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>Le porteur voit l'état de chaque pièce et le motif du refus.</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr"/>
+      <c r="I72" s="6" t="inlineStr"/>
+      <c r="J72" s="6" t="inlineStr"/>
+      <c r="K72" s="6" t="inlineStr"/>
+      <c r="L72" s="6" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>Porteur de projet</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Portail &gt; Pièces</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>Déposer un programme renommé en .pdf, puis un document Word à macros.</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>Fichiers d'essai fournis par le prestataire</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Dépôts refusés, formats acceptés rappelés (PDF, JPEG, PNG, DOCX, XLSX).</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr"/>
+      <c r="I73" s="7" t="inlineStr"/>
+      <c r="J73" s="7" t="inlineStr"/>
+      <c r="K73" s="7" t="inlineStr"/>
+      <c r="L73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Direction (société du groupe seule)</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>AxisPro Suite</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>Ouvrir AxisPro Suite avec un compte de direction ouvert à la seule société du groupe.</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>Aucun dossier, aucune pièce, revue ni grille du cabinet visible.</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr"/>
+      <c r="I74" s="6" t="inlineStr"/>
+      <c r="J74" s="6" t="inlineStr"/>
+      <c r="K74" s="6" t="inlineStr"/>
+      <c r="L74" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L62"/>
+  <autoFilter ref="A1:L74"/>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choisir OK, KO ou Réserve." type="list">
+    <dataValidation sqref="I2:I74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choisir OK, KO ou Réserve." type="list">
       <formula1>"OK,KO,Réserve"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3337,19 +3841,19 @@
         </is>
       </c>
       <c r="C2" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$62,"1")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$74,"1")</f>
         <v/>
       </c>
       <c r="D2" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"1",'Scénarios'!$I$2:$I$62,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"1",'Scénarios'!$I$2:$I$74,"OK")</f>
         <v/>
       </c>
       <c r="E2" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"1",'Scénarios'!$I$2:$I$62,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"1",'Scénarios'!$I$2:$I$74,"Réserve")</f>
         <v/>
       </c>
       <c r="F2" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"1",'Scénarios'!$I$2:$I$62,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"1",'Scénarios'!$I$2:$I$74,"KO")</f>
         <v/>
       </c>
       <c r="G2" s="9">
@@ -3369,19 +3873,19 @@
         </is>
       </c>
       <c r="C3" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$62,"2")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$74,"2")</f>
         <v/>
       </c>
       <c r="D3" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"2",'Scénarios'!$I$2:$I$62,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"2",'Scénarios'!$I$2:$I$74,"OK")</f>
         <v/>
       </c>
       <c r="E3" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"2",'Scénarios'!$I$2:$I$62,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"2",'Scénarios'!$I$2:$I$74,"Réserve")</f>
         <v/>
       </c>
       <c r="F3" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"2",'Scénarios'!$I$2:$I$62,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"2",'Scénarios'!$I$2:$I$74,"KO")</f>
         <v/>
       </c>
       <c r="G3" s="10">
@@ -3401,19 +3905,19 @@
         </is>
       </c>
       <c r="C4" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$62,"3")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$74,"3")</f>
         <v/>
       </c>
       <c r="D4" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"3",'Scénarios'!$I$2:$I$62,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"3",'Scénarios'!$I$2:$I$74,"OK")</f>
         <v/>
       </c>
       <c r="E4" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"3",'Scénarios'!$I$2:$I$62,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"3",'Scénarios'!$I$2:$I$74,"Réserve")</f>
         <v/>
       </c>
       <c r="F4" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"3",'Scénarios'!$I$2:$I$62,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"3",'Scénarios'!$I$2:$I$74,"KO")</f>
         <v/>
       </c>
       <c r="G4" s="9">
@@ -3433,19 +3937,19 @@
         </is>
       </c>
       <c r="C5" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$62,"4")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$74,"4")</f>
         <v/>
       </c>
       <c r="D5" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"4",'Scénarios'!$I$2:$I$62,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"4",'Scénarios'!$I$2:$I$74,"OK")</f>
         <v/>
       </c>
       <c r="E5" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"4",'Scénarios'!$I$2:$I$62,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"4",'Scénarios'!$I$2:$I$74,"Réserve")</f>
         <v/>
       </c>
       <c r="F5" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"4",'Scénarios'!$I$2:$I$62,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"4",'Scénarios'!$I$2:$I$74,"KO")</f>
         <v/>
       </c>
       <c r="G5" s="10">
@@ -3465,19 +3969,19 @@
         </is>
       </c>
       <c r="C6" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$62,"5")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$74,"5")</f>
         <v/>
       </c>
       <c r="D6" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"5",'Scénarios'!$I$2:$I$62,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"5",'Scénarios'!$I$2:$I$74,"OK")</f>
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"5",'Scénarios'!$I$2:$I$62,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"5",'Scénarios'!$I$2:$I$74,"Réserve")</f>
         <v/>
       </c>
       <c r="F6" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"5",'Scénarios'!$I$2:$I$62,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"5",'Scénarios'!$I$2:$I$74,"KO")</f>
         <v/>
       </c>
       <c r="G6" s="9">
@@ -3497,19 +4001,19 @@
         </is>
       </c>
       <c r="C7" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$62,"6")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$74,"6")</f>
         <v/>
       </c>
       <c r="D7" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"6",'Scénarios'!$I$2:$I$62,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"6",'Scénarios'!$I$2:$I$74,"OK")</f>
         <v/>
       </c>
       <c r="E7" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"6",'Scénarios'!$I$2:$I$62,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"6",'Scénarios'!$I$2:$I$74,"Réserve")</f>
         <v/>
       </c>
       <c r="F7" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"6",'Scénarios'!$I$2:$I$62,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"6",'Scénarios'!$I$2:$I$74,"KO")</f>
         <v/>
       </c>
       <c r="G7" s="10">
@@ -3529,19 +4033,19 @@
         </is>
       </c>
       <c r="C8" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$62,"7")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$74,"7")</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"7",'Scénarios'!$I$2:$I$62,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"7",'Scénarios'!$I$2:$I$74,"OK")</f>
         <v/>
       </c>
       <c r="E8" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"7",'Scénarios'!$I$2:$I$62,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"7",'Scénarios'!$I$2:$I$74,"Réserve")</f>
         <v/>
       </c>
       <c r="F8" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"7",'Scénarios'!$I$2:$I$62,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"7",'Scénarios'!$I$2:$I$74,"KO")</f>
         <v/>
       </c>
       <c r="G8" s="9">
@@ -3561,19 +4065,19 @@
         </is>
       </c>
       <c r="C9" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$62,"8")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$74,"8")</f>
         <v/>
       </c>
       <c r="D9" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"8",'Scénarios'!$I$2:$I$62,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"8",'Scénarios'!$I$2:$I$74,"OK")</f>
         <v/>
       </c>
       <c r="E9" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"8",'Scénarios'!$I$2:$I$62,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"8",'Scénarios'!$I$2:$I$74,"Réserve")</f>
         <v/>
       </c>
       <c r="F9" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"8",'Scénarios'!$I$2:$I$62,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"8",'Scénarios'!$I$2:$I$74,"KO")</f>
         <v/>
       </c>
       <c r="G9" s="10">
@@ -3593,19 +4097,19 @@
         </is>
       </c>
       <c r="C10" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$62,"9")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$74,"9")</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"9",'Scénarios'!$I$2:$I$62,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"9",'Scénarios'!$I$2:$I$74,"OK")</f>
         <v/>
       </c>
       <c r="E10" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"9",'Scénarios'!$I$2:$I$62,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"9",'Scénarios'!$I$2:$I$74,"Réserve")</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"9",'Scénarios'!$I$2:$I$62,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"9",'Scénarios'!$I$2:$I$74,"KO")</f>
         <v/>
       </c>
       <c r="G10" s="9">
@@ -3625,19 +4129,19 @@
         </is>
       </c>
       <c r="C11" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$62,"10")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$74,"10")</f>
         <v/>
       </c>
       <c r="D11" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"10",'Scénarios'!$I$2:$I$62,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"10",'Scénarios'!$I$2:$I$74,"OK")</f>
         <v/>
       </c>
       <c r="E11" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"10",'Scénarios'!$I$2:$I$62,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"10",'Scénarios'!$I$2:$I$74,"Réserve")</f>
         <v/>
       </c>
       <c r="F11" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"10",'Scénarios'!$I$2:$I$62,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"10",'Scénarios'!$I$2:$I$74,"KO")</f>
         <v/>
       </c>
       <c r="G11" s="10">
@@ -3657,19 +4161,19 @@
         </is>
       </c>
       <c r="C12" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$62,"11")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$74,"11")</f>
         <v/>
       </c>
       <c r="D12" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"11",'Scénarios'!$I$2:$I$62,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"11",'Scénarios'!$I$2:$I$74,"OK")</f>
         <v/>
       </c>
       <c r="E12" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"11",'Scénarios'!$I$2:$I$62,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"11",'Scénarios'!$I$2:$I$74,"Réserve")</f>
         <v/>
       </c>
       <c r="F12" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"11",'Scénarios'!$I$2:$I$62,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"11",'Scénarios'!$I$2:$I$74,"KO")</f>
         <v/>
       </c>
       <c r="G12" s="9">
@@ -3689,19 +4193,19 @@
         </is>
       </c>
       <c r="C13" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$62,"12")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$74,"12")</f>
         <v/>
       </c>
       <c r="D13" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"12",'Scénarios'!$I$2:$I$62,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"12",'Scénarios'!$I$2:$I$74,"OK")</f>
         <v/>
       </c>
       <c r="E13" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"12",'Scénarios'!$I$2:$I$62,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"12",'Scénarios'!$I$2:$I$74,"Réserve")</f>
         <v/>
       </c>
       <c r="F13" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"12",'Scénarios'!$I$2:$I$62,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"12",'Scénarios'!$I$2:$I$74,"KO")</f>
         <v/>
       </c>
       <c r="G13" s="10">
@@ -3721,19 +4225,19 @@
         </is>
       </c>
       <c r="C14" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$62,"13")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$74,"13")</f>
         <v/>
       </c>
       <c r="D14" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"13",'Scénarios'!$I$2:$I$62,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"13",'Scénarios'!$I$2:$I$74,"OK")</f>
         <v/>
       </c>
       <c r="E14" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"13",'Scénarios'!$I$2:$I$62,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"13",'Scénarios'!$I$2:$I$74,"Réserve")</f>
         <v/>
       </c>
       <c r="F14" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"13",'Scénarios'!$I$2:$I$62,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"13",'Scénarios'!$I$2:$I$74,"KO")</f>
         <v/>
       </c>
       <c r="G14" s="9">
@@ -3753,19 +4257,19 @@
         </is>
       </c>
       <c r="C15" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$62,"14")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$74,"14")</f>
         <v/>
       </c>
       <c r="D15" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"14",'Scénarios'!$I$2:$I$62,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"14",'Scénarios'!$I$2:$I$74,"OK")</f>
         <v/>
       </c>
       <c r="E15" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"14",'Scénarios'!$I$2:$I$62,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"14",'Scénarios'!$I$2:$I$74,"Réserve")</f>
         <v/>
       </c>
       <c r="F15" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"14",'Scénarios'!$I$2:$I$62,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"14",'Scénarios'!$I$2:$I$74,"KO")</f>
         <v/>
       </c>
       <c r="G15" s="10">
@@ -3785,19 +4289,19 @@
         </is>
       </c>
       <c r="C16" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$62,"15")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$74,"15")</f>
         <v/>
       </c>
       <c r="D16" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"15",'Scénarios'!$I$2:$I$62,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"15",'Scénarios'!$I$2:$I$74,"OK")</f>
         <v/>
       </c>
       <c r="E16" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"15",'Scénarios'!$I$2:$I$62,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"15",'Scénarios'!$I$2:$I$74,"Réserve")</f>
         <v/>
       </c>
       <c r="F16" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"15",'Scénarios'!$I$2:$I$62,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"15",'Scénarios'!$I$2:$I$74,"KO")</f>
         <v/>
       </c>
       <c r="G16" s="9">
@@ -3817,19 +4321,19 @@
         </is>
       </c>
       <c r="C17" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$62,"16")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$74,"16")</f>
         <v/>
       </c>
       <c r="D17" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"16",'Scénarios'!$I$2:$I$62,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"16",'Scénarios'!$I$2:$I$74,"OK")</f>
         <v/>
       </c>
       <c r="E17" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"16",'Scénarios'!$I$2:$I$62,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"16",'Scénarios'!$I$2:$I$74,"Réserve")</f>
         <v/>
       </c>
       <c r="F17" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"16",'Scénarios'!$I$2:$I$62,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"16",'Scénarios'!$I$2:$I$74,"KO")</f>
         <v/>
       </c>
       <c r="G17" s="10">
@@ -3849,19 +4353,19 @@
         </is>
       </c>
       <c r="C18" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$62,"17")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$74,"17")</f>
         <v/>
       </c>
       <c r="D18" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"17",'Scénarios'!$I$2:$I$62,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"17",'Scénarios'!$I$2:$I$74,"OK")</f>
         <v/>
       </c>
       <c r="E18" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"17",'Scénarios'!$I$2:$I$62,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"17",'Scénarios'!$I$2:$I$74,"Réserve")</f>
         <v/>
       </c>
       <c r="F18" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"17",'Scénarios'!$I$2:$I$62,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"17",'Scénarios'!$I$2:$I$74,"KO")</f>
         <v/>
       </c>
       <c r="G18" s="9">
@@ -3881,19 +4385,19 @@
         </is>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$62,"18")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$74,"18")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"18",'Scénarios'!$I$2:$I$62,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"18",'Scénarios'!$I$2:$I$74,"OK")</f>
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"18",'Scénarios'!$I$2:$I$62,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"18",'Scénarios'!$I$2:$I$74,"Réserve")</f>
         <v/>
       </c>
       <c r="F19" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"18",'Scénarios'!$I$2:$I$62,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"18",'Scénarios'!$I$2:$I$74,"KO")</f>
         <v/>
       </c>
       <c r="G19" s="10">
@@ -3913,19 +4417,19 @@
         </is>
       </c>
       <c r="C20" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$62,"19")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$74,"19")</f>
         <v/>
       </c>
       <c r="D20" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"19",'Scénarios'!$I$2:$I$62,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"19",'Scénarios'!$I$2:$I$74,"OK")</f>
         <v/>
       </c>
       <c r="E20" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"19",'Scénarios'!$I$2:$I$62,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"19",'Scénarios'!$I$2:$I$74,"Réserve")</f>
         <v/>
       </c>
       <c r="F20" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"19",'Scénarios'!$I$2:$I$62,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"19",'Scénarios'!$I$2:$I$74,"KO")</f>
         <v/>
       </c>
       <c r="G20" s="9">
@@ -3945,19 +4449,19 @@
         </is>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$62,"AX")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$74,"AX")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"AX",'Scénarios'!$I$2:$I$62,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"AX",'Scénarios'!$I$2:$I$74,"OK")</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"AX",'Scénarios'!$I$2:$I$62,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"AX",'Scénarios'!$I$2:$I$74,"Réserve")</f>
         <v/>
       </c>
       <c r="F21" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$62,"AX",'Scénarios'!$I$2:$I$62,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"AX",'Scénarios'!$I$2:$I$74,"KO")</f>
         <v/>
       </c>
       <c r="G21" s="10">

--- a/docs/projet/Cahier_de_recette.xlsx
+++ b/docs/projet/Cahier_de_recette.xlsx
@@ -803,7 +803,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Passer d'EGUITRA GROUP SARLU à MB AxisPro Consulting, puis revenir.</t>
+          <t>Passer d'EGUITRA GROUP SARLU à MB AxisPro, puis revenir.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Le premier voit le sélecteur et les deux sociétés ; le second ne voit que MB AxisPro Consulting.</t>
+          <t>Le premier voit le sélecteur et les deux sociétés ; le second ne voit que MB AxisPro.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr"/>

--- a/docs/projet/Cahier_de_recette.xlsx
+++ b/docs/projet/Cahier_de_recette.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthèse" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Scénarios'!$A$1:$L$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Scénarios'!$A$1:$L$77</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Scénarios'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -617,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3261,12 +3261,12 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>R62</t>
+          <t>R63</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
@@ -3276,22 +3276,22 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Pilotage &gt; Trésorerie</t>
+          <t>Transport &gt; Routes et tarifs</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>Afficher les flux mensuels et la prévision ; régler une échéance d'emprunt depuis une ligne de relevé.</t>
+          <t>Renseigner les forfaits d'une route et le prix du carburant ; saisir une rotation, la valider, puis changer le prix.</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Emprunt repris</t>
+          <t>Route et ensemble existants</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>Encaissements, décaissements, cash net et solde par mois face au seuil ; échéance proposée au rapprochement, capital et intérêts comptabilisés une seule fois.</t>
+          <t>Coût standard et marge estimée affichés à la saisie ; après validation, un nouveau prix ne change pas la rotation ; rentabilité : coûts standard, déclarés et comptabilisés côte à côte.</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr"/>
@@ -3303,37 +3303,37 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>R64</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>AX</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>AxisPro &gt; Grille d'évaluation</t>
+          <t>Transport &gt; Flotte, Propriétaires</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Importer la grille officielle ; la vérifier ; la mettre en vigueur.</t>
+          <t>Déclarer un ensemble géré pour un propriétaire avec ses charges mensuelles ; créer une règle de 5 % pour la société et une commission de partenaire ; établir les relevés du mois.</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>Classeur du cabinet</t>
+          <t>Rotations validées sur l'ensemble</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>8 gates et leurs règles, 15 domaines, 111 critères (9 knock-outs), 42 pièces et 102 rattachements chargés ; version en vigueur.</t>
+          <t>Relevé : chiffre d'affaires, charges, marge, commissions, part du propriétaire ; PDF et Excel ; ensemble à l'arrêt : part négative.</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr"/>
@@ -3345,37 +3345,37 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>R65</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>AX</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>AxisPro &gt; Dossiers</t>
+          <t>Transport &gt; Propriétaires</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>Ouvrir un dossier.</t>
+          <t>Préparer les pièces d'un relevé, les consulter dans Achats et Ventes, puis rouvrir le relevé.</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Projet réel anonymisé</t>
+          <t>Relevé établi</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>Référence attribuée ; critères du premier gate à évaluer.</t>
+          <t>Facture d'achat du propriétaire (ou refacturation d'une part négative) et facture du partenaire en brouillon, imputées sur l'ensemble ; aucune pièce pour la part de la société ; rouvrir supprime les brouillons.</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr"/>
@@ -3387,37 +3387,37 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>A03</t>
+          <t>R62</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>AX</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>Dossier &gt; Évaluation</t>
+          <t>Pilotage &gt; Trésorerie</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Évaluer les critères en saisie guidée ; déclarer disponible un knock-out sans pièce, puis lui joindre une preuve avec sa date de validité.</t>
+          <t>Afficher les flux mensuels et la prévision ; régler une échéance d'emprunt depuis une ligne de relevé.</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Emprunt repris</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>Sans pièce, critère retenu « incomplet » (saisie inchangée) ; avec la preuve, retenu disponible ; Readiness, APD et Bankability recalculés ; pièce de la data room disponible.</t>
+          <t>Encaissements, décaissements, cash net et solde par mois face au seuil ; échéance proposée au rapprochement, capital et intérêts comptabilisés une seule fois.</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr"/>
@@ -3429,7 +3429,7 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>A01</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
@@ -3444,22 +3444,22 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Dossier &gt; Synthèse</t>
+          <t>AxisPro &gt; Grille d'évaluation</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>Contrôler les knock-outs et les actions prioritaires ; passer au gate suivant ; forcer un passage refusé avec un motif.</t>
+          <t>Importer la grille officielle ; la vérifier ; la mettre en vigueur.</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Classeur du cabinet</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>NO-GO si un knock-out est actif ; passage refusé avec ses motifs ; passage forcé inscrit au journal.</t>
+          <t>8 gates et leurs règles, 15 domaines, 111 critères (9 knock-outs), 42 pièces et 102 rattachements chargés ; version en vigueur.</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr"/>
@@ -3471,7 +3471,7 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>A05</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
@@ -3486,22 +3486,22 @@
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Dossier &gt; Comités</t>
+          <t>AxisPro &gt; Dossiers</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Sceller et verrouiller une décision HOLD motivée ; vérifier l'empreinte ; tenter de modifier le dossier ; ouvrir une nouvelle révision ; comparer deux revues.</t>
+          <t>Ouvrir un dossier.</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Projet réel anonymisé</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>Décision non modifiable, empreinte valide ; dossier figé jusqu'à la nouvelle révision ; comparaison des scores, gates et domaines.</t>
+          <t>Référence attribuée ; critères du premier gate à évaluer.</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr"/>
@@ -3513,7 +3513,7 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>A06</t>
+          <t>A03</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Dossier &gt; Rapport</t>
+          <t>Dossier &gt; Évaluation</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>Télécharger le rapport du comité (PDF), le classeur d'évaluation, la fiche d'évaluation (la modifier puis la réimporter), la data room (.zip) et les pièces à fournir.</t>
+          <t>Évaluer les critères en saisie guidée ; déclarer disponible un knock-out sans pièce, puis lui joindre une preuve avec sa date de validité.</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>Politique appliquée et empreinte rappelées ; classeur au plan du modèle du cabinet ; import précédé d'un aperçu des changements.</t>
+          <t>Sans pièce, critère retenu « incomplet » (saisie inchangée) ; avec la preuve, retenu disponible ; Readiness, APD et Bankability recalculés ; pièce de la data room disponible.</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr"/>
@@ -3555,7 +3555,7 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -3570,22 +3570,22 @@
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Dossier &gt; Temps et facturation</t>
+          <t>Dossier &gt; Synthèse</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Saisir des temps ; facturer les honoraires.</t>
+          <t>Contrôler les knock-outs et les actions prioritaires ; passer au gate suivant ; forcer un passage refusé avec un motif.</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>Taux horaire</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>Facture d'honoraires en brouillon dans la comptabilité du cabinet.</t>
+          <t>NO-GO si un knock-out est actif ; passage refusé avec ses motifs ; passage forcé inscrit au journal.</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr"/>
@@ -3597,7 +3597,7 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>A08</t>
+          <t>A05</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
@@ -3607,27 +3607,27 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Porteur de projet</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Portail</t>
+          <t>Dossier &gt; Comités</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>Première connexion ; déposer une pièce ; écrire au cabinet.</t>
+          <t>Sceller et verrouiller une décision HOLD motivée ; vérifier l'empreinte ; tenter de modifier le dossier ; ouvrir une nouvelle révision ; comparer deux revues.</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>Accès ouvert par le cabinet</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>Pièce visible du cabinet ; notes internes du cabinet invisibles du porteur.</t>
+          <t>Décision non modifiable, empreinte valide ; dossier figé jusqu'à la nouvelle révision ; comparaison des scores, gates et domaines.</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr"/>
@@ -3639,7 +3639,7 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>A09</t>
+          <t>A06</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>Dossier &gt; Data room</t>
+          <t>Dossier &gt; Rapport</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Valider une pièce ; en refuser une autre avec un motif.</t>
+          <t>Télécharger le rapport du comité (PDF), le classeur d'évaluation, la fiche d'évaluation (la modifier puis la réimporter), la data room (.zip) et les pièces à fournir.</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>Le porteur voit l'état de chaque pièce et le motif du refus.</t>
+          <t>Politique appliquée et empreinte rappelées ; classeur au plan du modèle du cabinet ; import précédé d'un aperçu des changements.</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr"/>
@@ -3681,7 +3681,7 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A07</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
@@ -3691,27 +3691,27 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Porteur de projet</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Portail &gt; Pièces</t>
+          <t>Dossier &gt; Temps et facturation</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>Déposer un programme renommé en .pdf, puis un document Word à macros.</t>
+          <t>Saisir des temps ; facturer les honoraires.</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Fichiers d'essai fournis par le prestataire</t>
+          <t>Taux horaire</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>Dépôts refusés, formats acceptés rappelés (PDF, JPEG, PNG, DOCX, XLSX).</t>
+          <t>Facture d'honoraires en brouillon dans la comptabilité du cabinet.</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr"/>
@@ -3723,7 +3723,7 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>A08</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
@@ -3733,27 +3733,27 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>Direction (société du groupe seule)</t>
+          <t>Porteur de projet</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>AxisPro Suite</t>
+          <t>Portail</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Ouvrir AxisPro Suite avec un compte de direction ouvert à la seule société du groupe.</t>
+          <t>Première connexion ; déposer une pièce ; écrire au cabinet.</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Accès ouvert par le cabinet</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>Aucun dossier, aucune pièce, revue ni grille du cabinet visible.</t>
+          <t>Pièce visible du cabinet ; notes internes du cabinet invisibles du porteur.</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr"/>
@@ -3762,10 +3762,136 @@
       <c r="K74" s="6" t="inlineStr"/>
       <c r="L74" s="6" t="inlineStr"/>
     </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>Cabinet</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>Dossier &gt; Data room</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>Valider une pièce ; en refuser une autre avec un motif.</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>Le porteur voit l'état de chaque pièce et le motif du refus.</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr"/>
+      <c r="I75" s="7" t="inlineStr"/>
+      <c r="J75" s="7" t="inlineStr"/>
+      <c r="K75" s="7" t="inlineStr"/>
+      <c r="L75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>Porteur de projet</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Portail &gt; Pièces</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>Déposer un programme renommé en .pdf, puis un document Word à macros.</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>Fichiers d'essai fournis par le prestataire</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>Dépôts refusés, formats acceptés rappelés (PDF, JPEG, PNG, DOCX, XLSX).</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr"/>
+      <c r="I76" s="6" t="inlineStr"/>
+      <c r="J76" s="6" t="inlineStr"/>
+      <c r="K76" s="6" t="inlineStr"/>
+      <c r="L76" s="6" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Direction (société du groupe seule)</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>AxisPro Suite</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>Ouvrir AxisPro Suite avec un compte de direction ouvert à la seule société du groupe.</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>Aucun dossier, aucune pièce, revue ni grille du cabinet visible.</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr"/>
+      <c r="I77" s="7" t="inlineStr"/>
+      <c r="J77" s="7" t="inlineStr"/>
+      <c r="K77" s="7" t="inlineStr"/>
+      <c r="L77" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L74"/>
+  <autoFilter ref="A1:L77"/>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choisir OK, KO ou Réserve." type="list">
+    <dataValidation sqref="I2:I77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choisir OK, KO ou Réserve." type="list">
       <formula1>"OK,KO,Réserve"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3841,19 +3967,19 @@
         </is>
       </c>
       <c r="C2" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$74,"1")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$77,"1")</f>
         <v/>
       </c>
       <c r="D2" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"1",'Scénarios'!$I$2:$I$74,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"1",'Scénarios'!$I$2:$I$77,"OK")</f>
         <v/>
       </c>
       <c r="E2" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"1",'Scénarios'!$I$2:$I$74,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"1",'Scénarios'!$I$2:$I$77,"Réserve")</f>
         <v/>
       </c>
       <c r="F2" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"1",'Scénarios'!$I$2:$I$74,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"1",'Scénarios'!$I$2:$I$77,"KO")</f>
         <v/>
       </c>
       <c r="G2" s="9">
@@ -3873,19 +3999,19 @@
         </is>
       </c>
       <c r="C3" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$74,"2")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$77,"2")</f>
         <v/>
       </c>
       <c r="D3" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"2",'Scénarios'!$I$2:$I$74,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"2",'Scénarios'!$I$2:$I$77,"OK")</f>
         <v/>
       </c>
       <c r="E3" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"2",'Scénarios'!$I$2:$I$74,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"2",'Scénarios'!$I$2:$I$77,"Réserve")</f>
         <v/>
       </c>
       <c r="F3" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"2",'Scénarios'!$I$2:$I$74,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"2",'Scénarios'!$I$2:$I$77,"KO")</f>
         <v/>
       </c>
       <c r="G3" s="10">
@@ -3905,19 +4031,19 @@
         </is>
       </c>
       <c r="C4" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$74,"3")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$77,"3")</f>
         <v/>
       </c>
       <c r="D4" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"3",'Scénarios'!$I$2:$I$74,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"3",'Scénarios'!$I$2:$I$77,"OK")</f>
         <v/>
       </c>
       <c r="E4" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"3",'Scénarios'!$I$2:$I$74,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"3",'Scénarios'!$I$2:$I$77,"Réserve")</f>
         <v/>
       </c>
       <c r="F4" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"3",'Scénarios'!$I$2:$I$74,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"3",'Scénarios'!$I$2:$I$77,"KO")</f>
         <v/>
       </c>
       <c r="G4" s="9">
@@ -3937,19 +4063,19 @@
         </is>
       </c>
       <c r="C5" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$74,"4")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$77,"4")</f>
         <v/>
       </c>
       <c r="D5" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"4",'Scénarios'!$I$2:$I$74,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"4",'Scénarios'!$I$2:$I$77,"OK")</f>
         <v/>
       </c>
       <c r="E5" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"4",'Scénarios'!$I$2:$I$74,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"4",'Scénarios'!$I$2:$I$77,"Réserve")</f>
         <v/>
       </c>
       <c r="F5" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"4",'Scénarios'!$I$2:$I$74,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"4",'Scénarios'!$I$2:$I$77,"KO")</f>
         <v/>
       </c>
       <c r="G5" s="10">
@@ -3969,19 +4095,19 @@
         </is>
       </c>
       <c r="C6" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$74,"5")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$77,"5")</f>
         <v/>
       </c>
       <c r="D6" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"5",'Scénarios'!$I$2:$I$74,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"5",'Scénarios'!$I$2:$I$77,"OK")</f>
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"5",'Scénarios'!$I$2:$I$74,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"5",'Scénarios'!$I$2:$I$77,"Réserve")</f>
         <v/>
       </c>
       <c r="F6" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"5",'Scénarios'!$I$2:$I$74,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"5",'Scénarios'!$I$2:$I$77,"KO")</f>
         <v/>
       </c>
       <c r="G6" s="9">
@@ -4001,19 +4127,19 @@
         </is>
       </c>
       <c r="C7" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$74,"6")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$77,"6")</f>
         <v/>
       </c>
       <c r="D7" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"6",'Scénarios'!$I$2:$I$74,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"6",'Scénarios'!$I$2:$I$77,"OK")</f>
         <v/>
       </c>
       <c r="E7" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"6",'Scénarios'!$I$2:$I$74,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"6",'Scénarios'!$I$2:$I$77,"Réserve")</f>
         <v/>
       </c>
       <c r="F7" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"6",'Scénarios'!$I$2:$I$74,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"6",'Scénarios'!$I$2:$I$77,"KO")</f>
         <v/>
       </c>
       <c r="G7" s="10">
@@ -4033,19 +4159,19 @@
         </is>
       </c>
       <c r="C8" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$74,"7")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$77,"7")</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"7",'Scénarios'!$I$2:$I$74,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"7",'Scénarios'!$I$2:$I$77,"OK")</f>
         <v/>
       </c>
       <c r="E8" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"7",'Scénarios'!$I$2:$I$74,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"7",'Scénarios'!$I$2:$I$77,"Réserve")</f>
         <v/>
       </c>
       <c r="F8" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"7",'Scénarios'!$I$2:$I$74,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"7",'Scénarios'!$I$2:$I$77,"KO")</f>
         <v/>
       </c>
       <c r="G8" s="9">
@@ -4065,19 +4191,19 @@
         </is>
       </c>
       <c r="C9" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$74,"8")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$77,"8")</f>
         <v/>
       </c>
       <c r="D9" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"8",'Scénarios'!$I$2:$I$74,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"8",'Scénarios'!$I$2:$I$77,"OK")</f>
         <v/>
       </c>
       <c r="E9" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"8",'Scénarios'!$I$2:$I$74,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"8",'Scénarios'!$I$2:$I$77,"Réserve")</f>
         <v/>
       </c>
       <c r="F9" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"8",'Scénarios'!$I$2:$I$74,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"8",'Scénarios'!$I$2:$I$77,"KO")</f>
         <v/>
       </c>
       <c r="G9" s="10">
@@ -4097,19 +4223,19 @@
         </is>
       </c>
       <c r="C10" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$74,"9")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$77,"9")</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"9",'Scénarios'!$I$2:$I$74,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"9",'Scénarios'!$I$2:$I$77,"OK")</f>
         <v/>
       </c>
       <c r="E10" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"9",'Scénarios'!$I$2:$I$74,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"9",'Scénarios'!$I$2:$I$77,"Réserve")</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"9",'Scénarios'!$I$2:$I$74,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"9",'Scénarios'!$I$2:$I$77,"KO")</f>
         <v/>
       </c>
       <c r="G10" s="9">
@@ -4129,19 +4255,19 @@
         </is>
       </c>
       <c r="C11" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$74,"10")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$77,"10")</f>
         <v/>
       </c>
       <c r="D11" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"10",'Scénarios'!$I$2:$I$74,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"10",'Scénarios'!$I$2:$I$77,"OK")</f>
         <v/>
       </c>
       <c r="E11" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"10",'Scénarios'!$I$2:$I$74,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"10",'Scénarios'!$I$2:$I$77,"Réserve")</f>
         <v/>
       </c>
       <c r="F11" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"10",'Scénarios'!$I$2:$I$74,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"10",'Scénarios'!$I$2:$I$77,"KO")</f>
         <v/>
       </c>
       <c r="G11" s="10">
@@ -4161,19 +4287,19 @@
         </is>
       </c>
       <c r="C12" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$74,"11")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$77,"11")</f>
         <v/>
       </c>
       <c r="D12" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"11",'Scénarios'!$I$2:$I$74,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"11",'Scénarios'!$I$2:$I$77,"OK")</f>
         <v/>
       </c>
       <c r="E12" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"11",'Scénarios'!$I$2:$I$74,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"11",'Scénarios'!$I$2:$I$77,"Réserve")</f>
         <v/>
       </c>
       <c r="F12" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"11",'Scénarios'!$I$2:$I$74,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"11",'Scénarios'!$I$2:$I$77,"KO")</f>
         <v/>
       </c>
       <c r="G12" s="9">
@@ -4193,19 +4319,19 @@
         </is>
       </c>
       <c r="C13" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$74,"12")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$77,"12")</f>
         <v/>
       </c>
       <c r="D13" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"12",'Scénarios'!$I$2:$I$74,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"12",'Scénarios'!$I$2:$I$77,"OK")</f>
         <v/>
       </c>
       <c r="E13" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"12",'Scénarios'!$I$2:$I$74,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"12",'Scénarios'!$I$2:$I$77,"Réserve")</f>
         <v/>
       </c>
       <c r="F13" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"12",'Scénarios'!$I$2:$I$74,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"12",'Scénarios'!$I$2:$I$77,"KO")</f>
         <v/>
       </c>
       <c r="G13" s="10">
@@ -4225,19 +4351,19 @@
         </is>
       </c>
       <c r="C14" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$74,"13")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$77,"13")</f>
         <v/>
       </c>
       <c r="D14" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"13",'Scénarios'!$I$2:$I$74,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"13",'Scénarios'!$I$2:$I$77,"OK")</f>
         <v/>
       </c>
       <c r="E14" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"13",'Scénarios'!$I$2:$I$74,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"13",'Scénarios'!$I$2:$I$77,"Réserve")</f>
         <v/>
       </c>
       <c r="F14" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"13",'Scénarios'!$I$2:$I$74,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"13",'Scénarios'!$I$2:$I$77,"KO")</f>
         <v/>
       </c>
       <c r="G14" s="9">
@@ -4257,19 +4383,19 @@
         </is>
       </c>
       <c r="C15" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$74,"14")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$77,"14")</f>
         <v/>
       </c>
       <c r="D15" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"14",'Scénarios'!$I$2:$I$74,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"14",'Scénarios'!$I$2:$I$77,"OK")</f>
         <v/>
       </c>
       <c r="E15" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"14",'Scénarios'!$I$2:$I$74,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"14",'Scénarios'!$I$2:$I$77,"Réserve")</f>
         <v/>
       </c>
       <c r="F15" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"14",'Scénarios'!$I$2:$I$74,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"14",'Scénarios'!$I$2:$I$77,"KO")</f>
         <v/>
       </c>
       <c r="G15" s="10">
@@ -4289,19 +4415,19 @@
         </is>
       </c>
       <c r="C16" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$74,"15")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$77,"15")</f>
         <v/>
       </c>
       <c r="D16" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"15",'Scénarios'!$I$2:$I$74,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"15",'Scénarios'!$I$2:$I$77,"OK")</f>
         <v/>
       </c>
       <c r="E16" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"15",'Scénarios'!$I$2:$I$74,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"15",'Scénarios'!$I$2:$I$77,"Réserve")</f>
         <v/>
       </c>
       <c r="F16" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"15",'Scénarios'!$I$2:$I$74,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"15",'Scénarios'!$I$2:$I$77,"KO")</f>
         <v/>
       </c>
       <c r="G16" s="9">
@@ -4321,19 +4447,19 @@
         </is>
       </c>
       <c r="C17" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$74,"16")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$77,"16")</f>
         <v/>
       </c>
       <c r="D17" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"16",'Scénarios'!$I$2:$I$74,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"16",'Scénarios'!$I$2:$I$77,"OK")</f>
         <v/>
       </c>
       <c r="E17" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"16",'Scénarios'!$I$2:$I$74,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"16",'Scénarios'!$I$2:$I$77,"Réserve")</f>
         <v/>
       </c>
       <c r="F17" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"16",'Scénarios'!$I$2:$I$74,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"16",'Scénarios'!$I$2:$I$77,"KO")</f>
         <v/>
       </c>
       <c r="G17" s="10">
@@ -4353,19 +4479,19 @@
         </is>
       </c>
       <c r="C18" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$74,"17")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$77,"17")</f>
         <v/>
       </c>
       <c r="D18" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"17",'Scénarios'!$I$2:$I$74,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"17",'Scénarios'!$I$2:$I$77,"OK")</f>
         <v/>
       </c>
       <c r="E18" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"17",'Scénarios'!$I$2:$I$74,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"17",'Scénarios'!$I$2:$I$77,"Réserve")</f>
         <v/>
       </c>
       <c r="F18" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"17",'Scénarios'!$I$2:$I$74,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"17",'Scénarios'!$I$2:$I$77,"KO")</f>
         <v/>
       </c>
       <c r="G18" s="9">
@@ -4385,19 +4511,19 @@
         </is>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$74,"18")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$77,"18")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"18",'Scénarios'!$I$2:$I$74,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"18",'Scénarios'!$I$2:$I$77,"OK")</f>
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"18",'Scénarios'!$I$2:$I$74,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"18",'Scénarios'!$I$2:$I$77,"Réserve")</f>
         <v/>
       </c>
       <c r="F19" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"18",'Scénarios'!$I$2:$I$74,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"18",'Scénarios'!$I$2:$I$77,"KO")</f>
         <v/>
       </c>
       <c r="G19" s="10">
@@ -4417,19 +4543,19 @@
         </is>
       </c>
       <c r="C20" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$74,"19")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$77,"19")</f>
         <v/>
       </c>
       <c r="D20" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"19",'Scénarios'!$I$2:$I$74,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"19",'Scénarios'!$I$2:$I$77,"OK")</f>
         <v/>
       </c>
       <c r="E20" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"19",'Scénarios'!$I$2:$I$74,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"19",'Scénarios'!$I$2:$I$77,"Réserve")</f>
         <v/>
       </c>
       <c r="F20" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"19",'Scénarios'!$I$2:$I$74,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"19",'Scénarios'!$I$2:$I$77,"KO")</f>
         <v/>
       </c>
       <c r="G20" s="9">
@@ -4449,19 +4575,19 @@
         </is>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$74,"AX")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$77,"AX")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"AX",'Scénarios'!$I$2:$I$74,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"AX",'Scénarios'!$I$2:$I$77,"OK")</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"AX",'Scénarios'!$I$2:$I$74,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"AX",'Scénarios'!$I$2:$I$77,"Réserve")</f>
         <v/>
       </c>
       <c r="F21" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$74,"AX",'Scénarios'!$I$2:$I$74,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"AX",'Scénarios'!$I$2:$I$77,"KO")</f>
         <v/>
       </c>
       <c r="G21" s="10">

--- a/docs/projet/Cahier_de_recette.xlsx
+++ b/docs/projet/Cahier_de_recette.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthèse" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Scénarios'!$A$1:$L$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Scénarios'!$A$1:$L$80</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Scénarios'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -617,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3449,17 +3449,17 @@
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>Importer la grille officielle ; la vérifier ; la mettre en vigueur.</t>
+          <t>Importer l'outil de scoring du cabinet tel quel (version 3) ; le vérifier ; le mettre en vigueur.</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>Classeur du cabinet</t>
+          <t>Outil de scoring du cabinet (classeur)</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>8 gates et leurs règles, 15 domaines, 111 critères (9 knock-outs), 42 pièces et 102 rattachements chargés ; version en vigueur.</t>
+          <t>7 gates et leurs règles (complétude minimale de 40 % au gate 1), 8 compartiments, 14 domaines, 104 critères (9 knock-outs), 39 pièces rattachées ; codes repris de la version précédente ; knock-out incomplet non bloquant, non applicable à 1 point ; version en vigueur.</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr"/>
@@ -3888,10 +3888,136 @@
       <c r="K77" s="7" t="inlineStr"/>
       <c r="L77" s="7" t="inlineStr"/>
     </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Cabinet</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Dossier &gt; Synthèse, Évaluation</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>Confier deux compartiments à deux consultants ; filtrer la check-list sur « Mes compartiments » avec chacun.</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>Deux comptes cabinet</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>Suivi par compartiment : score, critères, manques, études renseignées, consultant ; chaque consultant ne voit que ses critères ; changements inscrits au journal.</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr"/>
+      <c r="I78" s="6" t="inlineStr"/>
+      <c r="J78" s="6" t="inlineStr"/>
+      <c r="K78" s="6" t="inlineStr"/>
+      <c r="L78" s="6" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>A13</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Cabinet</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Dossier &gt; Stage gates</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>Évaluer quelques critères du gate 1 en dessous de 40 % de complétude, puis au-dessus.</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>Dossier ouvert</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>Gate 1 en HOLD avec le motif de complétude, puis GO ou CONDITIONAL GO selon le score.</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr"/>
+      <c r="I79" s="7" t="inlineStr"/>
+      <c r="J79" s="7" t="inlineStr"/>
+      <c r="K79" s="7" t="inlineStr"/>
+      <c r="L79" s="7" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>A14</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>Cabinet</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Dossier &gt; Évaluation &gt; Importer une fiche</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>Remplir l'outil de scoring du cabinet hors ligne (statuts, études à produire) et l'importer dans un dossier.</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>Outil du cabinet rempli</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>Aperçu des changements, puis statuts et études à produire repris ; notices de l'outil ignorées.</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr"/>
+      <c r="I80" s="6" t="inlineStr"/>
+      <c r="J80" s="6" t="inlineStr"/>
+      <c r="K80" s="6" t="inlineStr"/>
+      <c r="L80" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L77"/>
+  <autoFilter ref="A1:L80"/>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choisir OK, KO ou Réserve." type="list">
+    <dataValidation sqref="I2:I80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choisir OK, KO ou Réserve." type="list">
       <formula1>"OK,KO,Réserve"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3967,19 +4093,19 @@
         </is>
       </c>
       <c r="C2" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$77,"1")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$80,"1")</f>
         <v/>
       </c>
       <c r="D2" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"1",'Scénarios'!$I$2:$I$77,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"1",'Scénarios'!$I$2:$I$80,"OK")</f>
         <v/>
       </c>
       <c r="E2" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"1",'Scénarios'!$I$2:$I$77,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"1",'Scénarios'!$I$2:$I$80,"Réserve")</f>
         <v/>
       </c>
       <c r="F2" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"1",'Scénarios'!$I$2:$I$77,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"1",'Scénarios'!$I$2:$I$80,"KO")</f>
         <v/>
       </c>
       <c r="G2" s="9">
@@ -3999,19 +4125,19 @@
         </is>
       </c>
       <c r="C3" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$77,"2")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$80,"2")</f>
         <v/>
       </c>
       <c r="D3" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"2",'Scénarios'!$I$2:$I$77,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"2",'Scénarios'!$I$2:$I$80,"OK")</f>
         <v/>
       </c>
       <c r="E3" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"2",'Scénarios'!$I$2:$I$77,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"2",'Scénarios'!$I$2:$I$80,"Réserve")</f>
         <v/>
       </c>
       <c r="F3" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"2",'Scénarios'!$I$2:$I$77,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"2",'Scénarios'!$I$2:$I$80,"KO")</f>
         <v/>
       </c>
       <c r="G3" s="10">
@@ -4031,19 +4157,19 @@
         </is>
       </c>
       <c r="C4" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$77,"3")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$80,"3")</f>
         <v/>
       </c>
       <c r="D4" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"3",'Scénarios'!$I$2:$I$77,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"3",'Scénarios'!$I$2:$I$80,"OK")</f>
         <v/>
       </c>
       <c r="E4" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"3",'Scénarios'!$I$2:$I$77,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"3",'Scénarios'!$I$2:$I$80,"Réserve")</f>
         <v/>
       </c>
       <c r="F4" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"3",'Scénarios'!$I$2:$I$77,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"3",'Scénarios'!$I$2:$I$80,"KO")</f>
         <v/>
       </c>
       <c r="G4" s="9">
@@ -4063,19 +4189,19 @@
         </is>
       </c>
       <c r="C5" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$77,"4")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$80,"4")</f>
         <v/>
       </c>
       <c r="D5" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"4",'Scénarios'!$I$2:$I$77,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"4",'Scénarios'!$I$2:$I$80,"OK")</f>
         <v/>
       </c>
       <c r="E5" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"4",'Scénarios'!$I$2:$I$77,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"4",'Scénarios'!$I$2:$I$80,"Réserve")</f>
         <v/>
       </c>
       <c r="F5" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"4",'Scénarios'!$I$2:$I$77,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"4",'Scénarios'!$I$2:$I$80,"KO")</f>
         <v/>
       </c>
       <c r="G5" s="10">
@@ -4095,19 +4221,19 @@
         </is>
       </c>
       <c r="C6" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$77,"5")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$80,"5")</f>
         <v/>
       </c>
       <c r="D6" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"5",'Scénarios'!$I$2:$I$77,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"5",'Scénarios'!$I$2:$I$80,"OK")</f>
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"5",'Scénarios'!$I$2:$I$77,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"5",'Scénarios'!$I$2:$I$80,"Réserve")</f>
         <v/>
       </c>
       <c r="F6" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"5",'Scénarios'!$I$2:$I$77,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"5",'Scénarios'!$I$2:$I$80,"KO")</f>
         <v/>
       </c>
       <c r="G6" s="9">
@@ -4127,19 +4253,19 @@
         </is>
       </c>
       <c r="C7" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$77,"6")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$80,"6")</f>
         <v/>
       </c>
       <c r="D7" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"6",'Scénarios'!$I$2:$I$77,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"6",'Scénarios'!$I$2:$I$80,"OK")</f>
         <v/>
       </c>
       <c r="E7" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"6",'Scénarios'!$I$2:$I$77,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"6",'Scénarios'!$I$2:$I$80,"Réserve")</f>
         <v/>
       </c>
       <c r="F7" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"6",'Scénarios'!$I$2:$I$77,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"6",'Scénarios'!$I$2:$I$80,"KO")</f>
         <v/>
       </c>
       <c r="G7" s="10">
@@ -4159,19 +4285,19 @@
         </is>
       </c>
       <c r="C8" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$77,"7")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$80,"7")</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"7",'Scénarios'!$I$2:$I$77,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"7",'Scénarios'!$I$2:$I$80,"OK")</f>
         <v/>
       </c>
       <c r="E8" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"7",'Scénarios'!$I$2:$I$77,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"7",'Scénarios'!$I$2:$I$80,"Réserve")</f>
         <v/>
       </c>
       <c r="F8" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"7",'Scénarios'!$I$2:$I$77,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"7",'Scénarios'!$I$2:$I$80,"KO")</f>
         <v/>
       </c>
       <c r="G8" s="9">
@@ -4191,19 +4317,19 @@
         </is>
       </c>
       <c r="C9" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$77,"8")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$80,"8")</f>
         <v/>
       </c>
       <c r="D9" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"8",'Scénarios'!$I$2:$I$77,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"8",'Scénarios'!$I$2:$I$80,"OK")</f>
         <v/>
       </c>
       <c r="E9" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"8",'Scénarios'!$I$2:$I$77,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"8",'Scénarios'!$I$2:$I$80,"Réserve")</f>
         <v/>
       </c>
       <c r="F9" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"8",'Scénarios'!$I$2:$I$77,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"8",'Scénarios'!$I$2:$I$80,"KO")</f>
         <v/>
       </c>
       <c r="G9" s="10">
@@ -4223,19 +4349,19 @@
         </is>
       </c>
       <c r="C10" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$77,"9")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$80,"9")</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"9",'Scénarios'!$I$2:$I$77,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"9",'Scénarios'!$I$2:$I$80,"OK")</f>
         <v/>
       </c>
       <c r="E10" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"9",'Scénarios'!$I$2:$I$77,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"9",'Scénarios'!$I$2:$I$80,"Réserve")</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"9",'Scénarios'!$I$2:$I$77,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"9",'Scénarios'!$I$2:$I$80,"KO")</f>
         <v/>
       </c>
       <c r="G10" s="9">
@@ -4255,19 +4381,19 @@
         </is>
       </c>
       <c r="C11" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$77,"10")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$80,"10")</f>
         <v/>
       </c>
       <c r="D11" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"10",'Scénarios'!$I$2:$I$77,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"10",'Scénarios'!$I$2:$I$80,"OK")</f>
         <v/>
       </c>
       <c r="E11" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"10",'Scénarios'!$I$2:$I$77,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"10",'Scénarios'!$I$2:$I$80,"Réserve")</f>
         <v/>
       </c>
       <c r="F11" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"10",'Scénarios'!$I$2:$I$77,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"10",'Scénarios'!$I$2:$I$80,"KO")</f>
         <v/>
       </c>
       <c r="G11" s="10">
@@ -4287,19 +4413,19 @@
         </is>
       </c>
       <c r="C12" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$77,"11")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$80,"11")</f>
         <v/>
       </c>
       <c r="D12" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"11",'Scénarios'!$I$2:$I$77,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"11",'Scénarios'!$I$2:$I$80,"OK")</f>
         <v/>
       </c>
       <c r="E12" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"11",'Scénarios'!$I$2:$I$77,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"11",'Scénarios'!$I$2:$I$80,"Réserve")</f>
         <v/>
       </c>
       <c r="F12" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"11",'Scénarios'!$I$2:$I$77,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"11",'Scénarios'!$I$2:$I$80,"KO")</f>
         <v/>
       </c>
       <c r="G12" s="9">
@@ -4319,19 +4445,19 @@
         </is>
       </c>
       <c r="C13" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$77,"12")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$80,"12")</f>
         <v/>
       </c>
       <c r="D13" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"12",'Scénarios'!$I$2:$I$77,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"12",'Scénarios'!$I$2:$I$80,"OK")</f>
         <v/>
       </c>
       <c r="E13" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"12",'Scénarios'!$I$2:$I$77,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"12",'Scénarios'!$I$2:$I$80,"Réserve")</f>
         <v/>
       </c>
       <c r="F13" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"12",'Scénarios'!$I$2:$I$77,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"12",'Scénarios'!$I$2:$I$80,"KO")</f>
         <v/>
       </c>
       <c r="G13" s="10">
@@ -4351,19 +4477,19 @@
         </is>
       </c>
       <c r="C14" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$77,"13")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$80,"13")</f>
         <v/>
       </c>
       <c r="D14" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"13",'Scénarios'!$I$2:$I$77,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"13",'Scénarios'!$I$2:$I$80,"OK")</f>
         <v/>
       </c>
       <c r="E14" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"13",'Scénarios'!$I$2:$I$77,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"13",'Scénarios'!$I$2:$I$80,"Réserve")</f>
         <v/>
       </c>
       <c r="F14" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"13",'Scénarios'!$I$2:$I$77,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"13",'Scénarios'!$I$2:$I$80,"KO")</f>
         <v/>
       </c>
       <c r="G14" s="9">
@@ -4383,19 +4509,19 @@
         </is>
       </c>
       <c r="C15" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$77,"14")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$80,"14")</f>
         <v/>
       </c>
       <c r="D15" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"14",'Scénarios'!$I$2:$I$77,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"14",'Scénarios'!$I$2:$I$80,"OK")</f>
         <v/>
       </c>
       <c r="E15" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"14",'Scénarios'!$I$2:$I$77,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"14",'Scénarios'!$I$2:$I$80,"Réserve")</f>
         <v/>
       </c>
       <c r="F15" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"14",'Scénarios'!$I$2:$I$77,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"14",'Scénarios'!$I$2:$I$80,"KO")</f>
         <v/>
       </c>
       <c r="G15" s="10">
@@ -4415,19 +4541,19 @@
         </is>
       </c>
       <c r="C16" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$77,"15")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$80,"15")</f>
         <v/>
       </c>
       <c r="D16" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"15",'Scénarios'!$I$2:$I$77,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"15",'Scénarios'!$I$2:$I$80,"OK")</f>
         <v/>
       </c>
       <c r="E16" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"15",'Scénarios'!$I$2:$I$77,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"15",'Scénarios'!$I$2:$I$80,"Réserve")</f>
         <v/>
       </c>
       <c r="F16" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"15",'Scénarios'!$I$2:$I$77,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"15",'Scénarios'!$I$2:$I$80,"KO")</f>
         <v/>
       </c>
       <c r="G16" s="9">
@@ -4447,19 +4573,19 @@
         </is>
       </c>
       <c r="C17" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$77,"16")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$80,"16")</f>
         <v/>
       </c>
       <c r="D17" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"16",'Scénarios'!$I$2:$I$77,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"16",'Scénarios'!$I$2:$I$80,"OK")</f>
         <v/>
       </c>
       <c r="E17" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"16",'Scénarios'!$I$2:$I$77,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"16",'Scénarios'!$I$2:$I$80,"Réserve")</f>
         <v/>
       </c>
       <c r="F17" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"16",'Scénarios'!$I$2:$I$77,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"16",'Scénarios'!$I$2:$I$80,"KO")</f>
         <v/>
       </c>
       <c r="G17" s="10">
@@ -4479,19 +4605,19 @@
         </is>
       </c>
       <c r="C18" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$77,"17")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$80,"17")</f>
         <v/>
       </c>
       <c r="D18" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"17",'Scénarios'!$I$2:$I$77,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"17",'Scénarios'!$I$2:$I$80,"OK")</f>
         <v/>
       </c>
       <c r="E18" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"17",'Scénarios'!$I$2:$I$77,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"17",'Scénarios'!$I$2:$I$80,"Réserve")</f>
         <v/>
       </c>
       <c r="F18" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"17",'Scénarios'!$I$2:$I$77,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"17",'Scénarios'!$I$2:$I$80,"KO")</f>
         <v/>
       </c>
       <c r="G18" s="9">
@@ -4511,19 +4637,19 @@
         </is>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$77,"18")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$80,"18")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"18",'Scénarios'!$I$2:$I$77,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"18",'Scénarios'!$I$2:$I$80,"OK")</f>
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"18",'Scénarios'!$I$2:$I$77,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"18",'Scénarios'!$I$2:$I$80,"Réserve")</f>
         <v/>
       </c>
       <c r="F19" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"18",'Scénarios'!$I$2:$I$77,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"18",'Scénarios'!$I$2:$I$80,"KO")</f>
         <v/>
       </c>
       <c r="G19" s="10">
@@ -4543,19 +4669,19 @@
         </is>
       </c>
       <c r="C20" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$77,"19")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$80,"19")</f>
         <v/>
       </c>
       <c r="D20" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"19",'Scénarios'!$I$2:$I$77,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"19",'Scénarios'!$I$2:$I$80,"OK")</f>
         <v/>
       </c>
       <c r="E20" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"19",'Scénarios'!$I$2:$I$77,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"19",'Scénarios'!$I$2:$I$80,"Réserve")</f>
         <v/>
       </c>
       <c r="F20" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"19",'Scénarios'!$I$2:$I$77,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"19",'Scénarios'!$I$2:$I$80,"KO")</f>
         <v/>
       </c>
       <c r="G20" s="9">
@@ -4575,19 +4701,19 @@
         </is>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$77,"AX")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$80,"AX")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"AX",'Scénarios'!$I$2:$I$77,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"AX",'Scénarios'!$I$2:$I$80,"OK")</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"AX",'Scénarios'!$I$2:$I$77,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"AX",'Scénarios'!$I$2:$I$80,"Réserve")</f>
         <v/>
       </c>
       <c r="F21" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$77,"AX",'Scénarios'!$I$2:$I$77,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"AX",'Scénarios'!$I$2:$I$80,"KO")</f>
         <v/>
       </c>
       <c r="G21" s="10">

--- a/docs/projet/Cahier_de_recette.xlsx
+++ b/docs/projet/Cahier_de_recette.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthèse" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Scénarios'!$A$1:$L$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Scénarios'!$A$1:$L$81</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Scénarios'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -617,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L80"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3387,37 +3387,37 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>R62</t>
+          <t>R66</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Exploitation</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>Pilotage &gt; Trésorerie</t>
+          <t>Accueil NIMOVA &gt; Transport</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Afficher les flux mensuels et la prévision ; régler une échéance d'emprunt depuis une ligne de relevé.</t>
+          <t>Ouvrir l'application Transport depuis l'accueil, puis passer d'un menu à l'autre (Exploitation, Gestion, Référentiels) ; ouvrir l'ancienne adresse /finance/transport.</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>Emprunt repris</t>
+          <t>Compte exploitation et compte finance</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>Encaissements, décaissements, cash net et solde par mois face au seuil ; échéance proposée au rapprochement, capital et intérêts comptabilisés une seule fois.</t>
+          <t>Application à part entière, aux couleurs du transport ; le parc ne voit pas Propriétaires et répartition ; l'ancienne adresse mène à l'application Transport.</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr"/>
@@ -3429,37 +3429,37 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>R62</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>AX</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>AxisPro &gt; Grille d'évaluation</t>
+          <t>Pilotage &gt; Trésorerie</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>Importer l'outil de scoring du cabinet tel quel (version 3) ; le vérifier ; le mettre en vigueur.</t>
+          <t>Afficher les flux mensuels et la prévision ; régler une échéance d'emprunt depuis une ligne de relevé.</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>Outil de scoring du cabinet (classeur)</t>
+          <t>Emprunt repris</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>7 gates et leurs règles (complétude minimale de 40 % au gate 1), 8 compartiments, 14 domaines, 104 critères (9 knock-outs), 39 pièces rattachées ; codes repris de la version précédente ; knock-out incomplet non bloquant, non applicable à 1 point ; version en vigueur.</t>
+          <t>Encaissements, décaissements, cash net et solde par mois face au seuil ; échéance proposée au rapprochement, capital et intérêts comptabilisés une seule fois.</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr"/>
@@ -3471,7 +3471,7 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>A01</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
@@ -3486,22 +3486,22 @@
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>AxisPro &gt; Dossiers</t>
+          <t>AxisPro &gt; Grille d'évaluation</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Ouvrir un dossier.</t>
+          <t>Importer l'outil de scoring du cabinet tel quel (version 3) ; le vérifier ; le mettre en vigueur.</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>Projet réel anonymisé</t>
+          <t>Outil de scoring du cabinet (classeur)</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>Référence attribuée ; critères du premier gate à évaluer.</t>
+          <t>7 gates et leurs règles (complétude minimale de 40 % au gate 1), 8 compartiments, 14 domaines, 104 critères (9 knock-outs), 39 pièces rattachées ; codes repris de la version précédente ; knock-out incomplet non bloquant, non applicable à 1 point ; version en vigueur.</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr"/>
@@ -3513,7 +3513,7 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>A03</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
@@ -3528,22 +3528,22 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Dossier &gt; Évaluation</t>
+          <t>AxisPro &gt; Dossiers</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>Évaluer les critères en saisie guidée ; déclarer disponible un knock-out sans pièce, puis lui joindre une preuve avec sa date de validité.</t>
+          <t>Ouvrir un dossier.</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Projet réel anonymisé</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>Sans pièce, critère retenu « incomplet » (saisie inchangée) ; avec la preuve, retenu disponible ; Readiness, APD et Bankability recalculés ; pièce de la data room disponible.</t>
+          <t>Référence attribuée ; critères du premier gate à évaluer.</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr"/>
@@ -3555,7 +3555,7 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>A03</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Dossier &gt; Synthèse</t>
+          <t>Dossier &gt; Évaluation</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Contrôler les knock-outs et les actions prioritaires ; passer au gate suivant ; forcer un passage refusé avec un motif.</t>
+          <t>Évaluer les critères en saisie guidée ; déclarer disponible un knock-out sans pièce, puis lui joindre une preuve avec sa date de validité.</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>NO-GO si un knock-out est actif ; passage refusé avec ses motifs ; passage forcé inscrit au journal.</t>
+          <t>Sans pièce, critère retenu « incomplet » (saisie inchangée) ; avec la preuve, retenu disponible ; Readiness, APD et Bankability recalculés ; pièce de la data room disponible.</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr"/>
@@ -3597,7 +3597,7 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>A05</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Dossier &gt; Comités</t>
+          <t>Dossier &gt; Synthèse</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>Sceller et verrouiller une décision HOLD motivée ; vérifier l'empreinte ; tenter de modifier le dossier ; ouvrir une nouvelle révision ; comparer deux revues.</t>
+          <t>Contrôler les knock-outs et les actions prioritaires ; passer au gate suivant ; forcer un passage refusé avec un motif.</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>Décision non modifiable, empreinte valide ; dossier figé jusqu'à la nouvelle révision ; comparaison des scores, gates et domaines.</t>
+          <t>NO-GO si un knock-out est actif ; passage refusé avec ses motifs ; passage forcé inscrit au journal.</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr"/>
@@ -3639,7 +3639,7 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>A06</t>
+          <t>A05</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>Dossier &gt; Rapport</t>
+          <t>Dossier &gt; Comités</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Télécharger le rapport du comité (PDF), le classeur d'évaluation, la fiche d'évaluation (la modifier puis la réimporter), la data room (.zip) et les pièces à fournir.</t>
+          <t>Sceller et verrouiller une décision HOLD motivée ; vérifier l'empreinte ; tenter de modifier le dossier ; ouvrir une nouvelle révision ; comparer deux revues.</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>Politique appliquée et empreinte rappelées ; classeur au plan du modèle du cabinet ; import précédé d'un aperçu des changements.</t>
+          <t>Décision non modifiable, empreinte valide ; dossier figé jusqu'à la nouvelle révision ; comparaison des scores, gates et domaines.</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr"/>
@@ -3681,7 +3681,7 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>A06</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
@@ -3696,22 +3696,22 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Dossier &gt; Temps et facturation</t>
+          <t>Dossier &gt; Rapport</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>Saisir des temps ; facturer les honoraires.</t>
+          <t>Télécharger le rapport du comité (PDF), le classeur d'évaluation, la fiche d'évaluation (la modifier puis la réimporter), la data room (.zip) et les pièces à fournir.</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Taux horaire</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>Facture d'honoraires en brouillon dans la comptabilité du cabinet.</t>
+          <t>Politique appliquée et empreinte rappelées ; classeur au plan du modèle du cabinet ; import précédé d'un aperçu des changements.</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr"/>
@@ -3723,7 +3723,7 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>A08</t>
+          <t>A07</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
@@ -3733,27 +3733,27 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>Porteur de projet</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>Portail</t>
+          <t>Dossier &gt; Temps et facturation</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Première connexion ; déposer une pièce ; écrire au cabinet.</t>
+          <t>Saisir des temps ; facturer les honoraires.</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>Accès ouvert par le cabinet</t>
+          <t>Taux horaire</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>Pièce visible du cabinet ; notes internes du cabinet invisibles du porteur.</t>
+          <t>Facture d'honoraires en brouillon dans la comptabilité du cabinet.</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr"/>
@@ -3765,7 +3765,7 @@
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>A09</t>
+          <t>A08</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
@@ -3775,27 +3775,27 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Porteur de projet</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Dossier &gt; Data room</t>
+          <t>Portail</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>Valider une pièce ; en refuser une autre avec un motif.</t>
+          <t>Première connexion ; déposer une pièce ; écrire au cabinet.</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Accès ouvert par le cabinet</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>Le porteur voit l'état de chaque pièce et le motif du refus.</t>
+          <t>Pièce visible du cabinet ; notes internes du cabinet invisibles du porteur.</t>
         </is>
       </c>
       <c r="H75" s="7" t="inlineStr"/>
@@ -3807,7 +3807,7 @@
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A09</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
@@ -3817,27 +3817,27 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>Porteur de projet</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>Portail &gt; Pièces</t>
+          <t>Dossier &gt; Data room</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Déposer un programme renommé en .pdf, puis un document Word à macros.</t>
+          <t>Valider une pièce ; en refuser une autre avec un motif.</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>Fichiers d'essai fournis par le prestataire</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>Dépôts refusés, formats acceptés rappelés (PDF, JPEG, PNG, DOCX, XLSX).</t>
+          <t>Le porteur voit l'état de chaque pièce et le motif du refus.</t>
         </is>
       </c>
       <c r="H76" s="6" t="inlineStr"/>
@@ -3849,7 +3849,7 @@
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
@@ -3859,27 +3859,27 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>Direction (société du groupe seule)</t>
+          <t>Porteur de projet</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>AxisPro Suite</t>
+          <t>Portail &gt; Pièces</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>Ouvrir AxisPro Suite avec un compte de direction ouvert à la seule société du groupe.</t>
+          <t>Déposer un programme renommé en .pdf, puis un document Word à macros.</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fichiers d'essai fournis par le prestataire</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>Aucun dossier, aucune pièce, revue ni grille du cabinet visible.</t>
+          <t>Dépôts refusés, formats acceptés rappelés (PDF, JPEG, PNG, DOCX, XLSX).</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr"/>
@@ -3891,7 +3891,7 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>A12</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -3901,27 +3901,27 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Direction (société du groupe seule)</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>Dossier &gt; Synthèse, Évaluation</t>
+          <t>AxisPro Suite</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Confier deux compartiments à deux consultants ; filtrer la check-list sur « Mes compartiments » avec chacun.</t>
+          <t>Ouvrir AxisPro Suite avec un compte de direction ouvert à la seule société du groupe.</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>Deux comptes cabinet</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>Suivi par compartiment : score, critères, manques, études renseignées, consultant ; chaque consultant ne voit que ses critères ; changements inscrits au journal.</t>
+          <t>Aucun dossier, aucune pièce, revue ni grille du cabinet visible.</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr"/>
@@ -3933,7 +3933,7 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>A13</t>
+          <t>A12</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
@@ -3948,22 +3948,22 @@
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Dossier &gt; Stage gates</t>
+          <t>Dossier &gt; Synthèse, Évaluation</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>Évaluer quelques critères du gate 1 en dessous de 40 % de complétude, puis au-dessus.</t>
+          <t>Confier deux compartiments à deux consultants ; filtrer la check-list sur « Mes compartiments » avec chacun.</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>Dossier ouvert</t>
+          <t>Deux comptes cabinet</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>Gate 1 en HOLD avec le motif de complétude, puis GO ou CONDITIONAL GO selon le score.</t>
+          <t>Suivi par compartiment : score, critères, manques, études renseignées, consultant ; chaque consultant ne voit que ses critères ; changements inscrits au journal.</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr"/>
@@ -3975,7 +3975,7 @@
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>A14</t>
+          <t>A13</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
@@ -3990,22 +3990,22 @@
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>Dossier &gt; Évaluation &gt; Importer une fiche</t>
+          <t>Dossier &gt; Stage gates</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>Remplir l'outil de scoring du cabinet hors ligne (statuts, études à produire) et l'importer dans un dossier.</t>
+          <t>Évaluer quelques critères du gate 1 en dessous de 40 % de complétude, puis au-dessus.</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>Outil du cabinet rempli</t>
+          <t>Dossier ouvert</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>Aperçu des changements, puis statuts et études à produire repris ; notices de l'outil ignorées.</t>
+          <t>Gate 1 en HOLD avec le motif de complétude, puis GO ou CONDITIONAL GO selon le score.</t>
         </is>
       </c>
       <c r="H80" s="6" t="inlineStr"/>
@@ -4014,10 +4014,52 @@
       <c r="K80" s="6" t="inlineStr"/>
       <c r="L80" s="6" t="inlineStr"/>
     </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>A14</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>AX</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>Cabinet</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Dossier &gt; Évaluation &gt; Importer une fiche</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>Remplir l'outil de scoring du cabinet hors ligne (statuts, études à produire) et l'importer dans un dossier.</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>Outil du cabinet rempli</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>Aperçu des changements, puis statuts et études à produire repris ; notices de l'outil ignorées.</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr"/>
+      <c r="I81" s="7" t="inlineStr"/>
+      <c r="J81" s="7" t="inlineStr"/>
+      <c r="K81" s="7" t="inlineStr"/>
+      <c r="L81" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L80"/>
+  <autoFilter ref="A1:L81"/>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choisir OK, KO ou Réserve." type="list">
+    <dataValidation sqref="I2:I81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choisir OK, KO ou Réserve." type="list">
       <formula1>"OK,KO,Réserve"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4093,19 +4135,19 @@
         </is>
       </c>
       <c r="C2" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$80,"1")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$81,"1")</f>
         <v/>
       </c>
       <c r="D2" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"1",'Scénarios'!$I$2:$I$80,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"1",'Scénarios'!$I$2:$I$81,"OK")</f>
         <v/>
       </c>
       <c r="E2" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"1",'Scénarios'!$I$2:$I$80,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"1",'Scénarios'!$I$2:$I$81,"Réserve")</f>
         <v/>
       </c>
       <c r="F2" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"1",'Scénarios'!$I$2:$I$80,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"1",'Scénarios'!$I$2:$I$81,"KO")</f>
         <v/>
       </c>
       <c r="G2" s="9">
@@ -4125,19 +4167,19 @@
         </is>
       </c>
       <c r="C3" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$80,"2")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$81,"2")</f>
         <v/>
       </c>
       <c r="D3" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"2",'Scénarios'!$I$2:$I$80,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"2",'Scénarios'!$I$2:$I$81,"OK")</f>
         <v/>
       </c>
       <c r="E3" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"2",'Scénarios'!$I$2:$I$80,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"2",'Scénarios'!$I$2:$I$81,"Réserve")</f>
         <v/>
       </c>
       <c r="F3" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"2",'Scénarios'!$I$2:$I$80,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"2",'Scénarios'!$I$2:$I$81,"KO")</f>
         <v/>
       </c>
       <c r="G3" s="10">
@@ -4157,19 +4199,19 @@
         </is>
       </c>
       <c r="C4" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$80,"3")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$81,"3")</f>
         <v/>
       </c>
       <c r="D4" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"3",'Scénarios'!$I$2:$I$80,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"3",'Scénarios'!$I$2:$I$81,"OK")</f>
         <v/>
       </c>
       <c r="E4" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"3",'Scénarios'!$I$2:$I$80,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"3",'Scénarios'!$I$2:$I$81,"Réserve")</f>
         <v/>
       </c>
       <c r="F4" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"3",'Scénarios'!$I$2:$I$80,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"3",'Scénarios'!$I$2:$I$81,"KO")</f>
         <v/>
       </c>
       <c r="G4" s="9">
@@ -4189,19 +4231,19 @@
         </is>
       </c>
       <c r="C5" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$80,"4")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$81,"4")</f>
         <v/>
       </c>
       <c r="D5" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"4",'Scénarios'!$I$2:$I$80,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"4",'Scénarios'!$I$2:$I$81,"OK")</f>
         <v/>
       </c>
       <c r="E5" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"4",'Scénarios'!$I$2:$I$80,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"4",'Scénarios'!$I$2:$I$81,"Réserve")</f>
         <v/>
       </c>
       <c r="F5" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"4",'Scénarios'!$I$2:$I$80,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"4",'Scénarios'!$I$2:$I$81,"KO")</f>
         <v/>
       </c>
       <c r="G5" s="10">
@@ -4221,19 +4263,19 @@
         </is>
       </c>
       <c r="C6" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$80,"5")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$81,"5")</f>
         <v/>
       </c>
       <c r="D6" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"5",'Scénarios'!$I$2:$I$80,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"5",'Scénarios'!$I$2:$I$81,"OK")</f>
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"5",'Scénarios'!$I$2:$I$80,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"5",'Scénarios'!$I$2:$I$81,"Réserve")</f>
         <v/>
       </c>
       <c r="F6" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"5",'Scénarios'!$I$2:$I$80,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"5",'Scénarios'!$I$2:$I$81,"KO")</f>
         <v/>
       </c>
       <c r="G6" s="9">
@@ -4253,19 +4295,19 @@
         </is>
       </c>
       <c r="C7" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$80,"6")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$81,"6")</f>
         <v/>
       </c>
       <c r="D7" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"6",'Scénarios'!$I$2:$I$80,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"6",'Scénarios'!$I$2:$I$81,"OK")</f>
         <v/>
       </c>
       <c r="E7" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"6",'Scénarios'!$I$2:$I$80,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"6",'Scénarios'!$I$2:$I$81,"Réserve")</f>
         <v/>
       </c>
       <c r="F7" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"6",'Scénarios'!$I$2:$I$80,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"6",'Scénarios'!$I$2:$I$81,"KO")</f>
         <v/>
       </c>
       <c r="G7" s="10">
@@ -4285,19 +4327,19 @@
         </is>
       </c>
       <c r="C8" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$80,"7")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$81,"7")</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"7",'Scénarios'!$I$2:$I$80,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"7",'Scénarios'!$I$2:$I$81,"OK")</f>
         <v/>
       </c>
       <c r="E8" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"7",'Scénarios'!$I$2:$I$80,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"7",'Scénarios'!$I$2:$I$81,"Réserve")</f>
         <v/>
       </c>
       <c r="F8" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"7",'Scénarios'!$I$2:$I$80,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"7",'Scénarios'!$I$2:$I$81,"KO")</f>
         <v/>
       </c>
       <c r="G8" s="9">
@@ -4317,19 +4359,19 @@
         </is>
       </c>
       <c r="C9" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$80,"8")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$81,"8")</f>
         <v/>
       </c>
       <c r="D9" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"8",'Scénarios'!$I$2:$I$80,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"8",'Scénarios'!$I$2:$I$81,"OK")</f>
         <v/>
       </c>
       <c r="E9" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"8",'Scénarios'!$I$2:$I$80,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"8",'Scénarios'!$I$2:$I$81,"Réserve")</f>
         <v/>
       </c>
       <c r="F9" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"8",'Scénarios'!$I$2:$I$80,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"8",'Scénarios'!$I$2:$I$81,"KO")</f>
         <v/>
       </c>
       <c r="G9" s="10">
@@ -4349,19 +4391,19 @@
         </is>
       </c>
       <c r="C10" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$80,"9")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$81,"9")</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"9",'Scénarios'!$I$2:$I$80,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"9",'Scénarios'!$I$2:$I$81,"OK")</f>
         <v/>
       </c>
       <c r="E10" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"9",'Scénarios'!$I$2:$I$80,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"9",'Scénarios'!$I$2:$I$81,"Réserve")</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"9",'Scénarios'!$I$2:$I$80,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"9",'Scénarios'!$I$2:$I$81,"KO")</f>
         <v/>
       </c>
       <c r="G10" s="9">
@@ -4381,19 +4423,19 @@
         </is>
       </c>
       <c r="C11" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$80,"10")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$81,"10")</f>
         <v/>
       </c>
       <c r="D11" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"10",'Scénarios'!$I$2:$I$80,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"10",'Scénarios'!$I$2:$I$81,"OK")</f>
         <v/>
       </c>
       <c r="E11" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"10",'Scénarios'!$I$2:$I$80,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"10",'Scénarios'!$I$2:$I$81,"Réserve")</f>
         <v/>
       </c>
       <c r="F11" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"10",'Scénarios'!$I$2:$I$80,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"10",'Scénarios'!$I$2:$I$81,"KO")</f>
         <v/>
       </c>
       <c r="G11" s="10">
@@ -4413,19 +4455,19 @@
         </is>
       </c>
       <c r="C12" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$80,"11")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$81,"11")</f>
         <v/>
       </c>
       <c r="D12" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"11",'Scénarios'!$I$2:$I$80,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"11",'Scénarios'!$I$2:$I$81,"OK")</f>
         <v/>
       </c>
       <c r="E12" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"11",'Scénarios'!$I$2:$I$80,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"11",'Scénarios'!$I$2:$I$81,"Réserve")</f>
         <v/>
       </c>
       <c r="F12" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"11",'Scénarios'!$I$2:$I$80,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"11",'Scénarios'!$I$2:$I$81,"KO")</f>
         <v/>
       </c>
       <c r="G12" s="9">
@@ -4445,19 +4487,19 @@
         </is>
       </c>
       <c r="C13" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$80,"12")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$81,"12")</f>
         <v/>
       </c>
       <c r="D13" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"12",'Scénarios'!$I$2:$I$80,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"12",'Scénarios'!$I$2:$I$81,"OK")</f>
         <v/>
       </c>
       <c r="E13" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"12",'Scénarios'!$I$2:$I$80,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"12",'Scénarios'!$I$2:$I$81,"Réserve")</f>
         <v/>
       </c>
       <c r="F13" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"12",'Scénarios'!$I$2:$I$80,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"12",'Scénarios'!$I$2:$I$81,"KO")</f>
         <v/>
       </c>
       <c r="G13" s="10">
@@ -4477,19 +4519,19 @@
         </is>
       </c>
       <c r="C14" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$80,"13")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$81,"13")</f>
         <v/>
       </c>
       <c r="D14" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"13",'Scénarios'!$I$2:$I$80,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"13",'Scénarios'!$I$2:$I$81,"OK")</f>
         <v/>
       </c>
       <c r="E14" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"13",'Scénarios'!$I$2:$I$80,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"13",'Scénarios'!$I$2:$I$81,"Réserve")</f>
         <v/>
       </c>
       <c r="F14" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"13",'Scénarios'!$I$2:$I$80,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"13",'Scénarios'!$I$2:$I$81,"KO")</f>
         <v/>
       </c>
       <c r="G14" s="9">
@@ -4509,19 +4551,19 @@
         </is>
       </c>
       <c r="C15" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$80,"14")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$81,"14")</f>
         <v/>
       </c>
       <c r="D15" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"14",'Scénarios'!$I$2:$I$80,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"14",'Scénarios'!$I$2:$I$81,"OK")</f>
         <v/>
       </c>
       <c r="E15" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"14",'Scénarios'!$I$2:$I$80,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"14",'Scénarios'!$I$2:$I$81,"Réserve")</f>
         <v/>
       </c>
       <c r="F15" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"14",'Scénarios'!$I$2:$I$80,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"14",'Scénarios'!$I$2:$I$81,"KO")</f>
         <v/>
       </c>
       <c r="G15" s="10">
@@ -4541,19 +4583,19 @@
         </is>
       </c>
       <c r="C16" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$80,"15")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$81,"15")</f>
         <v/>
       </c>
       <c r="D16" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"15",'Scénarios'!$I$2:$I$80,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"15",'Scénarios'!$I$2:$I$81,"OK")</f>
         <v/>
       </c>
       <c r="E16" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"15",'Scénarios'!$I$2:$I$80,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"15",'Scénarios'!$I$2:$I$81,"Réserve")</f>
         <v/>
       </c>
       <c r="F16" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"15",'Scénarios'!$I$2:$I$80,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"15",'Scénarios'!$I$2:$I$81,"KO")</f>
         <v/>
       </c>
       <c r="G16" s="9">
@@ -4573,19 +4615,19 @@
         </is>
       </c>
       <c r="C17" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$80,"16")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$81,"16")</f>
         <v/>
       </c>
       <c r="D17" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"16",'Scénarios'!$I$2:$I$80,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"16",'Scénarios'!$I$2:$I$81,"OK")</f>
         <v/>
       </c>
       <c r="E17" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"16",'Scénarios'!$I$2:$I$80,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"16",'Scénarios'!$I$2:$I$81,"Réserve")</f>
         <v/>
       </c>
       <c r="F17" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"16",'Scénarios'!$I$2:$I$80,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"16",'Scénarios'!$I$2:$I$81,"KO")</f>
         <v/>
       </c>
       <c r="G17" s="10">
@@ -4605,19 +4647,19 @@
         </is>
       </c>
       <c r="C18" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$80,"17")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$81,"17")</f>
         <v/>
       </c>
       <c r="D18" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"17",'Scénarios'!$I$2:$I$80,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"17",'Scénarios'!$I$2:$I$81,"OK")</f>
         <v/>
       </c>
       <c r="E18" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"17",'Scénarios'!$I$2:$I$80,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"17",'Scénarios'!$I$2:$I$81,"Réserve")</f>
         <v/>
       </c>
       <c r="F18" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"17",'Scénarios'!$I$2:$I$80,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"17",'Scénarios'!$I$2:$I$81,"KO")</f>
         <v/>
       </c>
       <c r="G18" s="9">
@@ -4637,19 +4679,19 @@
         </is>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$80,"18")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$81,"18")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"18",'Scénarios'!$I$2:$I$80,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"18",'Scénarios'!$I$2:$I$81,"OK")</f>
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"18",'Scénarios'!$I$2:$I$80,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"18",'Scénarios'!$I$2:$I$81,"Réserve")</f>
         <v/>
       </c>
       <c r="F19" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"18",'Scénarios'!$I$2:$I$80,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"18",'Scénarios'!$I$2:$I$81,"KO")</f>
         <v/>
       </c>
       <c r="G19" s="10">
@@ -4669,19 +4711,19 @@
         </is>
       </c>
       <c r="C20" s="9">
-        <f>COUNTIF('Scénarios'!$B$2:$B$80,"19")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$81,"19")</f>
         <v/>
       </c>
       <c r="D20" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"19",'Scénarios'!$I$2:$I$80,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"19",'Scénarios'!$I$2:$I$81,"OK")</f>
         <v/>
       </c>
       <c r="E20" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"19",'Scénarios'!$I$2:$I$80,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"19",'Scénarios'!$I$2:$I$81,"Réserve")</f>
         <v/>
       </c>
       <c r="F20" s="9">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"19",'Scénarios'!$I$2:$I$80,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"19",'Scénarios'!$I$2:$I$81,"KO")</f>
         <v/>
       </c>
       <c r="G20" s="9">
@@ -4701,19 +4743,19 @@
         </is>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIF('Scénarios'!$B$2:$B$80,"AX")</f>
+        <f>COUNTIF('Scénarios'!$B$2:$B$81,"AX")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"AX",'Scénarios'!$I$2:$I$80,"OK")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"AX",'Scénarios'!$I$2:$I$81,"OK")</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"AX",'Scénarios'!$I$2:$I$80,"Réserve")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"AX",'Scénarios'!$I$2:$I$81,"Réserve")</f>
         <v/>
       </c>
       <c r="F21" s="10">
-        <f>COUNTIFS('Scénarios'!$B$2:$B$80,"AX",'Scénarios'!$I$2:$I$80,"KO")</f>
+        <f>COUNTIFS('Scénarios'!$B$2:$B$81,"AX",'Scénarios'!$I$2:$I$81,"KO")</f>
         <v/>
       </c>
       <c r="G21" s="10">
